--- a/data/export/2026-09-27-浦东35路.xlsx
+++ b/data/export/2026-09-27-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC10"/>
+  <dimension ref="A1:AC21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -715,7 +715,7 @@
       <c r="AB2" s="2" t="inlineStr"/>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
@@ -776,7 +776,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -826,7 +826,7 @@
       <c r="AB3" s="2" t="inlineStr"/>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
@@ -887,7 +887,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -937,7 +937,7 @@
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
@@ -998,7 +998,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1048,7 +1048,7 @@
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1159,7 +1159,7 @@
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
@@ -1220,7 +1220,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1270,7 +1270,7 @@
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1381,7 +1381,7 @@
       <c r="AB8" s="2" t="inlineStr"/>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
@@ -1442,7 +1442,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1492,7 +1492,7 @@
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
@@ -1553,7 +1553,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1603,7 +1603,1228 @@
       <c r="AB10" s="2" t="inlineStr"/>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr"/>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>沪A11062A</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr"/>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr"/>
+      <c r="R11" s="2" t="inlineStr"/>
+      <c r="S11" s="2" t="inlineStr"/>
+      <c r="T11" s="2" t="inlineStr"/>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y11" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z11" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB11" s="2" t="inlineStr"/>
+      <c r="AC11" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr"/>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>沪A71572D</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr"/>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr"/>
+      <c r="R12" s="2" t="inlineStr"/>
+      <c r="S12" s="2" t="inlineStr"/>
+      <c r="T12" s="2" t="inlineStr"/>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W12" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y12" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB12" s="2" t="inlineStr"/>
+      <c r="AC12" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr"/>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr"/>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr"/>
+      <c r="R13" s="2" t="inlineStr"/>
+      <c r="S13" s="2" t="inlineStr"/>
+      <c r="T13" s="2" t="inlineStr"/>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y13" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr"/>
+      <c r="AC13" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr"/>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>沪A02316D</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr"/>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr"/>
+      <c r="R14" s="2" t="inlineStr"/>
+      <c r="S14" s="2" t="inlineStr"/>
+      <c r="T14" s="2" t="inlineStr"/>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y14" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB14" s="2" t="inlineStr"/>
+      <c r="AC14" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr"/>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>沪A70597D</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr"/>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr"/>
+      <c r="R15" s="2" t="inlineStr"/>
+      <c r="S15" s="2" t="inlineStr"/>
+      <c r="T15" s="2" t="inlineStr"/>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W15" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y15" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z15" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB15" s="2" t="inlineStr"/>
+      <c r="AC15" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr"/>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>沪A37267D</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr"/>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr"/>
+      <c r="R16" s="2" t="inlineStr"/>
+      <c r="S16" s="2" t="inlineStr"/>
+      <c r="T16" s="2" t="inlineStr"/>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y16" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr"/>
+      <c r="AC16" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr"/>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>沪A09172D</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr"/>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr"/>
+      <c r="R17" s="2" t="inlineStr"/>
+      <c r="S17" s="2" t="inlineStr"/>
+      <c r="T17" s="2" t="inlineStr"/>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y17" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z17" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr"/>
+      <c r="AC17" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr"/>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>沪A95621D</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr"/>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr"/>
+      <c r="R18" s="2" t="inlineStr"/>
+      <c r="S18" s="2" t="inlineStr"/>
+      <c r="T18" s="2" t="inlineStr"/>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W18" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y18" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z18" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB18" s="2" t="inlineStr"/>
+      <c r="AC18" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr"/>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>沪A05218D</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr"/>
+      <c r="K19" s="2" t="inlineStr"/>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr"/>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr"/>
+      <c r="R19" s="2" t="inlineStr"/>
+      <c r="S19" s="2" t="inlineStr"/>
+      <c r="T19" s="2" t="inlineStr"/>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W19" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y19" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB19" s="2" t="inlineStr"/>
+      <c r="AC19" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr"/>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>沪A73927D</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr"/>
+      <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr"/>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr"/>
+      <c r="R20" s="2" t="inlineStr"/>
+      <c r="S20" s="2" t="inlineStr"/>
+      <c r="T20" s="2" t="inlineStr"/>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W20" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y20" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB20" s="2" t="inlineStr"/>
+      <c r="AC20" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr"/>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>沪A67057D</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr"/>
+      <c r="K21" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr"/>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr"/>
+      <c r="R21" s="2" t="inlineStr"/>
+      <c r="S21" s="2" t="inlineStr"/>
+      <c r="T21" s="2" t="inlineStr"/>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W21" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y21" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z21" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="inlineStr"/>
+      <c r="AC21" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-27-浦东35路.xlsx
+++ b/data/export/2026-09-27-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC21"/>
+  <dimension ref="A1:AC32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -441,7 +441,7 @@
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
     <col width="26" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="25" customWidth="1" min="12" max="12"/>
     <col width="22" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
@@ -632,32 +632,36 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -665,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -689,33 +693,37 @@
       </c>
       <c r="W2" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB2" s="2" t="inlineStr"/>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
+          <t>129.0</t>
+        </is>
+      </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -743,32 +751,36 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -776,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -800,33 +812,37 @@
       </c>
       <c r="W3" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y3" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" s="2" t="inlineStr"/>
+      <c r="AB3" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -854,32 +870,36 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>143分钟</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -887,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -911,17 +931,17 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z4" s="2" t="inlineStr">
@@ -931,13 +951,17 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB4" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
+          <t>143.0</t>
+        </is>
+      </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -965,32 +989,36 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:34</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>123分钟</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -998,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1022,33 +1050,37 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB5" s="2" t="inlineStr"/>
+      <c r="AB5" s="2" t="inlineStr">
+        <is>
+          <t>123.0</t>
+        </is>
+      </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
@@ -1109,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1159,7 +1191,7 @@
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -1220,7 +1252,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1270,7 +1302,7 @@
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -1298,32 +1330,36 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -1331,7 +1367,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1355,17 +1391,17 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z8" s="2" t="inlineStr">
@@ -1375,13 +1411,17 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB8" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB8" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -1442,7 +1482,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1492,7 +1532,7 @@
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -1553,7 +1593,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1603,7 +1643,7 @@
       <c r="AB10" s="2" t="inlineStr"/>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -1664,7 +1704,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1714,7 +1754,7 @@
       <c r="AB11" s="2" t="inlineStr"/>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -1775,7 +1815,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1825,7 +1865,7 @@
       <c r="AB12" s="2" t="inlineStr"/>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -1886,7 +1926,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1936,7 +1976,7 @@
       <c r="AB13" s="2" t="inlineStr"/>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -1997,7 +2037,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2047,7 +2087,7 @@
       <c r="AB14" s="2" t="inlineStr"/>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -2108,7 +2148,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2158,7 +2198,7 @@
       <c r="AB15" s="2" t="inlineStr"/>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -2219,7 +2259,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2269,7 +2309,7 @@
       <c r="AB16" s="2" t="inlineStr"/>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -2330,7 +2370,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2380,7 +2420,7 @@
       <c r="AB17" s="2" t="inlineStr"/>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -2441,7 +2481,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2491,7 +2531,7 @@
       <c r="AB18" s="2" t="inlineStr"/>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -2552,7 +2592,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2602,7 +2642,7 @@
       <c r="AB19" s="2" t="inlineStr"/>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -2663,7 +2703,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2713,7 +2753,7 @@
       <c r="AB20" s="2" t="inlineStr"/>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -2721,22 +2761,22 @@
       <c r="A21" s="2" t="inlineStr"/>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>沪A67057D</t>
+          <t>沪A36993D</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>07:54</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -2769,12 +2809,12 @@
       <c r="M21" s="2" t="inlineStr"/>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2824,7 +2864,1240 @@
       <c r="AB21" s="2" t="inlineStr"/>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr"/>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>沪A67057D</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr"/>
+      <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr"/>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr"/>
+      <c r="R22" s="2" t="inlineStr"/>
+      <c r="S22" s="2" t="inlineStr"/>
+      <c r="T22" s="2" t="inlineStr"/>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y22" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr"/>
+      <c r="AC22" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr"/>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>沪A51682D</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr"/>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr"/>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr"/>
+      <c r="R23" s="2" t="inlineStr"/>
+      <c r="S23" s="2" t="inlineStr"/>
+      <c r="T23" s="2" t="inlineStr"/>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y23" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr"/>
+      <c r="AC23" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr"/>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>沪A55102D</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr"/>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr"/>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr"/>
+      <c r="R24" s="2" t="inlineStr"/>
+      <c r="S24" s="2" t="inlineStr"/>
+      <c r="T24" s="2" t="inlineStr"/>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z24" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr"/>
+      <c r="AC24" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr"/>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>沪A15790A</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr"/>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr"/>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr"/>
+      <c r="R25" s="2" t="inlineStr"/>
+      <c r="S25" s="2" t="inlineStr"/>
+      <c r="T25" s="2" t="inlineStr"/>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr"/>
+      <c r="AC25" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr"/>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr"/>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr"/>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr"/>
+      <c r="R26" s="2" t="inlineStr"/>
+      <c r="S26" s="2" t="inlineStr"/>
+      <c r="T26" s="2" t="inlineStr"/>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr"/>
+      <c r="AC26" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr"/>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>沪A67672D</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>08:28</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr"/>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr"/>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr"/>
+      <c r="R27" s="2" t="inlineStr"/>
+      <c r="S27" s="2" t="inlineStr"/>
+      <c r="T27" s="2" t="inlineStr"/>
+      <c r="U27" s="2" t="inlineStr">
+        <is>
+          <t>08:28</t>
+        </is>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z27" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr"/>
+      <c r="AC27" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr"/>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>沪A62880D</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr"/>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr"/>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr"/>
+      <c r="R28" s="2" t="inlineStr"/>
+      <c r="S28" s="2" t="inlineStr"/>
+      <c r="T28" s="2" t="inlineStr"/>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr"/>
+      <c r="AC28" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr"/>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>沪A15330A</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>08:38</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr"/>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr"/>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr"/>
+      <c r="R29" s="2" t="inlineStr"/>
+      <c r="S29" s="2" t="inlineStr"/>
+      <c r="T29" s="2" t="inlineStr"/>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>08:38</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z29" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
+          <t>129.0</t>
+        </is>
+      </c>
+      <c r="AC29" s="2" t="inlineStr">
+        <is>
+          <t>4/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr"/>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>沪A02891D</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr"/>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr"/>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr"/>
+      <c r="R30" s="2" t="inlineStr"/>
+      <c r="S30" s="2" t="inlineStr"/>
+      <c r="T30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z30" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
+      <c r="AC30" s="2" t="inlineStr">
+        <is>
+          <t>2/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr"/>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>沪A67712D</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>08:48</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr"/>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr"/>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr"/>
+      <c r="R31" s="2" t="inlineStr"/>
+      <c r="S31" s="2" t="inlineStr"/>
+      <c r="T31" s="2" t="inlineStr"/>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
+          <t>08:48</t>
+        </is>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z31" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr"/>
+      <c r="AC31" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr"/>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>沪A65668D</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr"/>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr"/>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr"/>
+      <c r="R32" s="2" t="inlineStr"/>
+      <c r="S32" s="2" t="inlineStr"/>
+      <c r="T32" s="2" t="inlineStr"/>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z32" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
+          <t>123.0</t>
+        </is>
+      </c>
+      <c r="AC32" s="2" t="inlineStr">
+        <is>
+          <t>1/28</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-27-浦东35路.xlsx
+++ b/data/export/2026-09-27-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC32"/>
+  <dimension ref="A1:AC41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -436,7 +436,7 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="36" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
@@ -446,10 +446,10 @@
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
-    <col width="10" customWidth="1" min="17" max="17"/>
+    <col width="16" customWidth="1" min="17" max="17"/>
     <col width="16" customWidth="1" min="18" max="18"/>
     <col width="20" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="36" customWidth="1" min="20" max="20"/>
     <col width="14" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
     <col width="12" customWidth="1" min="23" max="23"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -880,24 +880,24 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>143分钟</t>
+          <t>137分钟</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,22 +946,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -999,24 +999,24 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>08:34</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>123分钟</t>
+          <t>122分钟</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1075,12 +1075,12 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>123.0</t>
+          <t>122.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>1/29</t>
         </is>
       </c>
     </row>
@@ -1108,32 +1108,36 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:36</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr"/>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -1141,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1165,33 +1169,37 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB6" s="2" t="inlineStr"/>
+      <c r="AB6" s="2" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1260,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1291,7 +1299,7 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
@@ -1302,7 +1310,7 @@
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -1340,12 +1348,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>128分钟</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
@@ -1367,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1406,22 +1414,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -1449,32 +1457,36 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -1482,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1506,33 +1518,37 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB9" s="2" t="inlineStr"/>
+      <c r="AB9" s="2" t="inlineStr">
+        <is>
+          <t>129.0</t>
+        </is>
+      </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -1560,32 +1576,36 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:07</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -1593,7 +1613,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1617,17 +1637,17 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z10" s="2" t="inlineStr">
@@ -1637,13 +1657,17 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB10" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB10" s="2" t="inlineStr">
+        <is>
+          <t>133.0</t>
+        </is>
+      </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -1671,32 +1695,36 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>135分钟</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
           <t>06:40</t>
@@ -1704,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1728,33 +1756,37 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB11" s="2" t="inlineStr"/>
+      <c r="AB11" s="2" t="inlineStr">
+        <is>
+          <t>135.0</t>
+        </is>
+      </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -1782,32 +1814,36 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
           <t>06:40</t>
@@ -1815,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1839,33 +1875,37 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB12" s="2" t="inlineStr"/>
+      <c r="AB12" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -1893,12 +1933,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程33%处后消失；随后反向物理轨迹由seq37推进至seq59，推进22站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1926,7 +1966,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1934,10 +1974,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q13" s="2" t="inlineStr"/>
-      <c r="R13" s="2" t="inlineStr"/>
-      <c r="S13" s="2" t="inlineStr"/>
-      <c r="T13" s="2" t="inlineStr"/>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>物理seq22（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>08:01</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>08:11</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq22映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±10分钟；反向位置浦建路锦绣路 ETA 9分钟参与校验</t>
+        </is>
+      </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
           <t>07:12</t>
@@ -1976,7 +2032,7 @@
       <c r="AB13" s="2" t="inlineStr"/>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -2037,7 +2093,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2087,7 +2143,7 @@
       <c r="AB14" s="2" t="inlineStr"/>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -2115,32 +2171,36 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr"/>
       <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -2148,7 +2208,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2172,33 +2232,37 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA15" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB15" s="2" t="inlineStr"/>
+      <c r="AB15" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -2226,12 +2290,12 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq42推进至seq53，推进11站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -2259,7 +2323,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2267,10 +2331,22 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q16" s="2" t="inlineStr"/>
-      <c r="R16" s="2" t="inlineStr"/>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>物理seq24（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>08:16</t>
+        </is>
+      </c>
       <c r="S16" s="2" t="inlineStr"/>
-      <c r="T16" s="2" t="inlineStr"/>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>区间折返已由主分类器确认；折返点按重建物理位置seq24映射；现有采样不足以把折返发车时间控制在±10分钟</t>
+        </is>
+      </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
           <t>07:24</t>
@@ -2309,7 +2385,7 @@
       <c r="AB16" s="2" t="inlineStr"/>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -2370,7 +2446,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2420,7 +2496,7 @@
       <c r="AB17" s="2" t="inlineStr"/>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -2481,7 +2557,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2531,7 +2607,7 @@
       <c r="AB18" s="2" t="inlineStr"/>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -2592,7 +2668,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2642,7 +2718,7 @@
       <c r="AB19" s="2" t="inlineStr"/>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -2703,7 +2779,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2753,7 +2829,7 @@
       <c r="AB20" s="2" t="inlineStr"/>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -2814,7 +2890,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2864,7 +2940,7 @@
       <c r="AB21" s="2" t="inlineStr"/>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -2925,7 +3001,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -2975,7 +3051,7 @@
       <c r="AB22" s="2" t="inlineStr"/>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3112,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3086,7 +3162,7 @@
       <c r="AB23" s="2" t="inlineStr"/>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -3147,7 +3223,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3197,7 +3273,7 @@
       <c r="AB24" s="2" t="inlineStr"/>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -3258,7 +3334,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3308,7 +3384,7 @@
       <c r="AB25" s="2" t="inlineStr"/>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -3369,7 +3445,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3419,7 +3495,7 @@
       <c r="AB26" s="2" t="inlineStr"/>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -3480,7 +3556,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3530,7 +3606,7 @@
       <c r="AB27" s="2" t="inlineStr"/>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -3591,7 +3667,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3641,7 +3717,7 @@
       <c r="AB28" s="2" t="inlineStr"/>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -3702,7 +3778,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3756,7 +3832,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -3817,7 +3893,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3871,7 +3947,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -3932,7 +4008,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -3982,7 +4058,7 @@
       <c r="AB31" s="2" t="inlineStr"/>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -3990,22 +4066,22 @@
       <c r="A32" s="2" t="inlineStr"/>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>沪A65668D</t>
+          <t>沪A62981D</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -4043,7 +4119,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4092,12 +4168,1039 @@
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>123.0</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>11/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr"/>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>沪A65668D</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr"/>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr"/>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr"/>
+      <c r="R33" s="2" t="inlineStr"/>
+      <c r="S33" s="2" t="inlineStr"/>
+      <c r="T33" s="2" t="inlineStr"/>
+      <c r="U33" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y33" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z33" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
+          <t>122.0</t>
+        </is>
+      </c>
+      <c r="AC33" s="2" t="inlineStr">
+        <is>
+          <t>1/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr"/>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>沪A68375D</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr"/>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr"/>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr"/>
+      <c r="R34" s="2" t="inlineStr"/>
+      <c r="S34" s="2" t="inlineStr"/>
+      <c r="T34" s="2" t="inlineStr"/>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y34" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z34" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
+      <c r="AC34" s="2" t="inlineStr">
+        <is>
+          <t>2/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr"/>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>沪A90275D</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr"/>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr"/>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr"/>
+      <c r="R35" s="2" t="inlineStr"/>
+      <c r="S35" s="2" t="inlineStr"/>
+      <c r="T35" s="2" t="inlineStr"/>
+      <c r="U35" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y35" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z35" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
+      <c r="AC35" s="2" t="inlineStr">
+        <is>
+          <t>3/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr"/>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>沪A62217D</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr"/>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr"/>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr"/>
+      <c r="R36" s="2" t="inlineStr"/>
+      <c r="S36" s="2" t="inlineStr"/>
+      <c r="T36" s="2" t="inlineStr"/>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z36" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr"/>
+      <c r="AC36" s="2" t="inlineStr">
+        <is>
+          <t>—/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr"/>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>沪A66883D</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr"/>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr"/>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr"/>
+      <c r="R37" s="2" t="inlineStr"/>
+      <c r="S37" s="2" t="inlineStr"/>
+      <c r="T37" s="2" t="inlineStr"/>
+      <c r="U37" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z37" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
+          <t>129.0</t>
+        </is>
+      </c>
+      <c r="AC37" s="2" t="inlineStr">
+        <is>
+          <t>6/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr"/>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>沪A79307D</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>09:38</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr"/>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr"/>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr"/>
+      <c r="R38" s="2" t="inlineStr"/>
+      <c r="S38" s="2" t="inlineStr"/>
+      <c r="T38" s="2" t="inlineStr"/>
+      <c r="U38" s="2" t="inlineStr">
+        <is>
+          <t>09:38</t>
+        </is>
+      </c>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z38" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr"/>
+      <c r="AC38" s="2" t="inlineStr">
+        <is>
+          <t>—/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr"/>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>沪A71572D</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr"/>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr"/>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr"/>
+      <c r="R39" s="2" t="inlineStr"/>
+      <c r="S39" s="2" t="inlineStr"/>
+      <c r="T39" s="2" t="inlineStr"/>
+      <c r="U39" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
+      <c r="AC39" s="2" t="inlineStr">
+        <is>
+          <t>8/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr"/>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>沪A11062A</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr"/>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr"/>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr"/>
+      <c r="R40" s="2" t="inlineStr"/>
+      <c r="S40" s="2" t="inlineStr"/>
+      <c r="T40" s="2" t="inlineStr"/>
+      <c r="U40" s="2" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W40" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y40" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z40" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB40" s="2" t="inlineStr">
+        <is>
+          <t>135.0</t>
+        </is>
+      </c>
+      <c r="AC40" s="2" t="inlineStr">
+        <is>
+          <t>10/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr"/>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>沪A70597D</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr"/>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr"/>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr"/>
+      <c r="R41" s="2" t="inlineStr"/>
+      <c r="S41" s="2" t="inlineStr"/>
+      <c r="T41" s="2" t="inlineStr"/>
+      <c r="U41" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W41" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y41" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z41" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB41" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
+      <c r="AC41" s="2" t="inlineStr">
+        <is>
+          <t>4/29</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-27-浦东35路.xlsx
+++ b/data/export/2026-09-27-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC41"/>
+  <dimension ref="A1:AC48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1375,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -1667,7 +1667,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -1732,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1786,7 +1786,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1905,7 +1905,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -2093,7 +2093,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2208,7 +2208,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2262,7 +2262,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -2295,7 +2295,7 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq42推进至seq53，推进11站，达到≥2站确认条件</t>
+          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq42推进至seq58，推进16站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -2323,7 +2323,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2485,7 +2485,7 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
@@ -2524,32 +2524,36 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -2557,7 +2561,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2581,33 +2585,37 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA18" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB18" s="2" t="inlineStr"/>
+      <c r="AB18" s="2" t="inlineStr">
+        <is>
+          <t>131.0</t>
+        </is>
+      </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -2635,32 +2643,36 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>123分钟</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr"/>
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
           <t>06:40</t>
@@ -2668,7 +2680,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2692,33 +2704,37 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB19" s="2" t="inlineStr"/>
+      <c r="AB19" s="2" t="inlineStr">
+        <is>
+          <t>123.0</t>
+        </is>
+      </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -2746,32 +2762,36 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>136分钟</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr"/>
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -2779,7 +2799,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2803,33 +2823,37 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB20" s="2" t="inlineStr"/>
+      <c r="AB20" s="2" t="inlineStr">
+        <is>
+          <t>136.0</t>
+        </is>
+      </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -2857,32 +2881,36 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr"/>
       <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
           <t>07:31</t>
@@ -2890,7 +2918,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2914,33 +2942,37 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y21" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA21" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB21" s="2" t="inlineStr"/>
+      <c r="AB21" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -2968,32 +3000,36 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr"/>
       <c r="K22" s="2" t="inlineStr"/>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -3001,7 +3037,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3025,33 +3061,37 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y22" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB22" s="2" t="inlineStr"/>
+      <c r="AB22" s="2" t="inlineStr">
+        <is>
+          <t>129.0</t>
+        </is>
+      </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -3079,32 +3119,36 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr"/>
       <c r="K23" s="2" t="inlineStr"/>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
           <t>06:40</t>
@@ -3112,7 +3156,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3136,17 +3180,17 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y23" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z23" s="2" t="inlineStr">
@@ -3156,13 +3200,17 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB23" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -3223,7 +3271,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3301,32 +3349,36 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr"/>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -3334,7 +3386,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3358,17 +3410,17 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr">
@@ -3378,13 +3430,17 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB25" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -3412,32 +3468,36 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr"/>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3445,7 +3505,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3469,17 +3529,17 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
@@ -3489,13 +3549,17 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB26" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
+          <t>132.0</t>
+        </is>
+      </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -3523,32 +3587,36 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr"/>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3556,7 +3624,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3580,17 +3648,17 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr">
@@ -3600,13 +3668,17 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB27" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
+          <t>131.0</t>
+        </is>
+      </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -3667,7 +3739,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3778,7 +3850,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3832,7 +3904,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -3893,7 +3965,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3947,7 +4019,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -4008,7 +4080,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4119,7 +4191,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4173,7 +4245,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -4234,7 +4306,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4349,7 +4421,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4403,7 +4475,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -4464,7 +4536,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4518,7 +4590,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -4579,7 +4651,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4690,7 +4762,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4744,7 +4816,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -4805,7 +4877,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4916,7 +4988,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -4970,7 +5042,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -5031,7 +5103,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5085,7 +5157,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -5146,7 +5218,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5200,7 +5272,804 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>6/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr"/>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>沪A02316D</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr"/>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr"/>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr"/>
+      <c r="R42" s="2" t="inlineStr"/>
+      <c r="S42" s="2" t="inlineStr"/>
+      <c r="T42" s="2" t="inlineStr"/>
+      <c r="U42" s="2" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z42" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB42" s="2" t="inlineStr"/>
+      <c r="AC42" s="2" t="inlineStr">
+        <is>
+          <t>—/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr"/>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>沪A95621D</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr"/>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr"/>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr"/>
+      <c r="R43" s="2" t="inlineStr"/>
+      <c r="S43" s="2" t="inlineStr"/>
+      <c r="T43" s="2" t="inlineStr"/>
+      <c r="U43" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W43" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y43" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z43" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB43" s="2" t="inlineStr">
+        <is>
+          <t>131.0</t>
+        </is>
+      </c>
+      <c r="AC43" s="2" t="inlineStr">
+        <is>
+          <t>14/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr"/>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>沪A09172D</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr"/>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr"/>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr"/>
+      <c r="R44" s="2" t="inlineStr"/>
+      <c r="S44" s="2" t="inlineStr"/>
+      <c r="T44" s="2" t="inlineStr"/>
+      <c r="U44" s="2" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W44" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y44" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z44" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB44" s="2" t="inlineStr"/>
+      <c r="AC44" s="2" t="inlineStr">
+        <is>
+          <t>—/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr"/>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>沪A73927D</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr"/>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr"/>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr"/>
+      <c r="R45" s="2" t="inlineStr"/>
+      <c r="S45" s="2" t="inlineStr"/>
+      <c r="T45" s="2" t="inlineStr"/>
+      <c r="U45" s="2" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W45" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z45" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB45" s="2" t="inlineStr">
+        <is>
+          <t>136.0</t>
+        </is>
+      </c>
+      <c r="AC45" s="2" t="inlineStr">
+        <is>
+          <t>19/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr"/>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>沪A05218D</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr"/>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr"/>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr"/>
+      <c r="R46" s="2" t="inlineStr"/>
+      <c r="S46" s="2" t="inlineStr"/>
+      <c r="T46" s="2" t="inlineStr"/>
+      <c r="U46" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z46" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB46" s="2" t="inlineStr">
+        <is>
+          <t>123.0</t>
+        </is>
+      </c>
+      <c r="AC46" s="2" t="inlineStr">
+        <is>
+          <t>2/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr"/>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>沪A36993D</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr"/>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr"/>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr"/>
+      <c r="R47" s="2" t="inlineStr"/>
+      <c r="S47" s="2" t="inlineStr"/>
+      <c r="T47" s="2" t="inlineStr"/>
+      <c r="U47" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W47" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y47" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z47" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB47" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
+      <c r="AC47" s="2" t="inlineStr">
+        <is>
+          <t>6/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr"/>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>沪A67057D</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr"/>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr"/>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr"/>
+      <c r="R48" s="2" t="inlineStr"/>
+      <c r="S48" s="2" t="inlineStr"/>
+      <c r="T48" s="2" t="inlineStr"/>
+      <c r="U48" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W48" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y48" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z48" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB48" s="2" t="inlineStr">
+        <is>
+          <t>129.0</t>
+        </is>
+      </c>
+      <c r="AC48" s="2" t="inlineStr">
+        <is>
+          <t>10/29</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-27-浦东35路.xlsx
+++ b/data/export/2026-09-27-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC48"/>
+  <dimension ref="A1:AC56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,17 +708,17 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>129.5</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -832,17 +832,17 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>132.5</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -951,17 +951,17 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,22 +1065,22 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>122.0</t>
+          <t>124.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>1/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1184,22 +1184,22 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA6" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1375,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1533,22 +1533,22 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA9" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>128.5</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -1667,7 +1667,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -1732,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1905,7 +1905,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -2093,7 +2093,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2208,7 +2208,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2262,7 +2262,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -2446,7 +2446,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2615,7 +2615,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>1/29</t>
         </is>
       </c>
     </row>
@@ -2799,7 +2799,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2918,7 +2918,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2972,7 +2972,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -3037,7 +3037,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3091,7 +3091,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -3156,7 +3156,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3195,14 +3195,14 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA23" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
           <t>126.0</t>
@@ -3210,7 +3210,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3425,14 +3425,14 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA25" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
           <t>128.0</t>
@@ -3440,7 +3440,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -3559,7 +3559,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -3597,12 +3597,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>131分钟</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr"/>
@@ -3624,7 +3624,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3673,12 +3673,12 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -3706,32 +3706,36 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>136分钟</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr"/>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3739,7 +3743,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3763,33 +3767,37 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA28" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB28" s="2" t="inlineStr"/>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
+          <t>136.0</t>
+        </is>
+      </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -3817,32 +3825,36 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr"/>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3850,7 +3862,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3874,32 +3886,32 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA29" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>129.5</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
@@ -3932,32 +3944,36 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>137分钟</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr"/>
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3965,7 +3981,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3989,17 +4005,17 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z30" s="2" t="inlineStr">
@@ -4009,17 +4025,17 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>132.5</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -4047,32 +4063,36 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>136分钟</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr"/>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M31" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
           <t>06:40</t>
@@ -4080,7 +4100,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4104,33 +4124,37 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA31" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB31" s="2" t="inlineStr"/>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
+          <t>136.0</t>
+        </is>
+      </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -4158,32 +4182,36 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>139分钟</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr"/>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4191,7 +4219,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4215,17 +4243,17 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z32" s="2" t="inlineStr">
@@ -4235,17 +4263,17 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -4273,32 +4301,36 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr"/>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M33" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4306,7 +4338,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4330,37 +4362,37 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA33" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>122.0</t>
+          <t>124.0</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>1/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -4388,32 +4420,36 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>139分钟</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr"/>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4421,7 +4457,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4445,37 +4481,37 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA34" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -4503,32 +4539,36 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr"/>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M35" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4536,7 +4576,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4560,17 +4600,17 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z35" s="2" t="inlineStr">
@@ -4580,7 +4620,7 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
@@ -4590,7 +4630,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -4651,7 +4691,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4729,32 +4769,36 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr"/>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M37" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -4762,7 +4806,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4786,37 +4830,37 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA37" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>128.5</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -4844,12 +4888,12 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程34%处后消失；随后反向物理轨迹由seq37推进至seq49，推进12站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -4877,7 +4921,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4885,10 +4929,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q38" s="2" t="inlineStr"/>
-      <c r="R38" s="2" t="inlineStr"/>
-      <c r="S38" s="2" t="inlineStr"/>
-      <c r="T38" s="2" t="inlineStr"/>
+      <c r="Q38" s="2" t="inlineStr">
+        <is>
+          <t>物理seq23（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R38" s="2" t="inlineStr">
+        <is>
+          <t>10:29</t>
+        </is>
+      </c>
+      <c r="S38" s="2" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="T38" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq23映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±6分钟；反向位置浦建路锦绣路 ETA 10分钟参与校验</t>
+        </is>
+      </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
           <t>09:38</t>
@@ -4988,7 +5048,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5042,7 +5102,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -5103,7 +5163,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5218,7 +5278,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5272,7 +5332,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -5333,7 +5393,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5444,7 +5504,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5498,7 +5558,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -5559,7 +5619,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5670,7 +5730,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5785,7 +5845,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5839,7 +5899,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>1/29</t>
         </is>
       </c>
     </row>
@@ -5900,7 +5960,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -5954,7 +6014,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -6015,7 +6075,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6069,7 +6129,927 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
+          <t>9/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr"/>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>沪A51682D</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr"/>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr"/>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="inlineStr"/>
+      <c r="R49" s="2" t="inlineStr"/>
+      <c r="S49" s="2" t="inlineStr"/>
+      <c r="T49" s="2" t="inlineStr"/>
+      <c r="U49" s="2" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="V49" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W49" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y49" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z49" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB49" s="2" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="AC49" s="2" t="inlineStr">
+        <is>
+          <t>3/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr"/>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>沪A15790A</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr"/>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr"/>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr"/>
+      <c r="R50" s="2" t="inlineStr"/>
+      <c r="S50" s="2" t="inlineStr"/>
+      <c r="T50" s="2" t="inlineStr"/>
+      <c r="U50" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="V50" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W50" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y50" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z50" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB50" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
+      <c r="AC50" s="2" t="inlineStr">
+        <is>
+          <t>5/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr"/>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>沪A62880D</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr"/>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr"/>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="inlineStr"/>
+      <c r="R51" s="2" t="inlineStr"/>
+      <c r="S51" s="2" t="inlineStr"/>
+      <c r="T51" s="2" t="inlineStr"/>
+      <c r="U51" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="V51" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W51" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y51" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z51" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB51" s="2" t="inlineStr">
+        <is>
+          <t>136.0</t>
+        </is>
+      </c>
+      <c r="AC51" s="2" t="inlineStr">
+        <is>
+          <t>19/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr"/>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>沪A15330A</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr"/>
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr"/>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr"/>
+      <c r="R52" s="2" t="inlineStr"/>
+      <c r="S52" s="2" t="inlineStr"/>
+      <c r="T52" s="2" t="inlineStr"/>
+      <c r="U52" s="2" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="V52" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W52" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y52" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z52" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB52" s="2" t="inlineStr">
+        <is>
+          <t>129.5</t>
+        </is>
+      </c>
+      <c r="AC52" s="2" t="inlineStr">
+        <is>
           <t>10/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr"/>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>沪A65668D</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr"/>
+      <c r="K53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr"/>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr"/>
+      <c r="R53" s="2" t="inlineStr"/>
+      <c r="S53" s="2" t="inlineStr"/>
+      <c r="T53" s="2" t="inlineStr"/>
+      <c r="U53" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="V53" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W53" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y53" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z53" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB53" s="2" t="inlineStr">
+        <is>
+          <t>124.0</t>
+        </is>
+      </c>
+      <c r="AC53" s="2" t="inlineStr">
+        <is>
+          <t>2/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr"/>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>沪A67712D</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr"/>
+      <c r="K54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr"/>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr"/>
+      <c r="R54" s="2" t="inlineStr"/>
+      <c r="S54" s="2" t="inlineStr"/>
+      <c r="T54" s="2" t="inlineStr"/>
+      <c r="U54" s="2" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="V54" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W54" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y54" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z54" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB54" s="2" t="inlineStr">
+        <is>
+          <t>136.0</t>
+        </is>
+      </c>
+      <c r="AC54" s="2" t="inlineStr">
+        <is>
+          <t>19/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr"/>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>沪A66883D</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr"/>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr"/>
+      <c r="N55" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="inlineStr"/>
+      <c r="R55" s="2" t="inlineStr"/>
+      <c r="S55" s="2" t="inlineStr"/>
+      <c r="T55" s="2" t="inlineStr"/>
+      <c r="U55" s="2" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="V55" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W55" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y55" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z55" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB55" s="2" t="inlineStr">
+        <is>
+          <t>128.5</t>
+        </is>
+      </c>
+      <c r="AC55" s="2" t="inlineStr">
+        <is>
+          <t>8/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr"/>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>沪A68375D</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr"/>
+      <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr"/>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr"/>
+      <c r="R56" s="2" t="inlineStr"/>
+      <c r="S56" s="2" t="inlineStr"/>
+      <c r="T56" s="2" t="inlineStr"/>
+      <c r="U56" s="2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="V56" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W56" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y56" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z56" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB56" s="2" t="inlineStr">
+        <is>
+          <t>132.0</t>
+        </is>
+      </c>
+      <c r="AC56" s="2" t="inlineStr">
+        <is>
+          <t>13/29</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-27-浦东35路.xlsx
+++ b/data/export/2026-09-27-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC56"/>
+  <dimension ref="A1:AC61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1194,12 +1194,12 @@
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1304,13 +1304,17 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB7" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB7" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1498,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1543,7 +1547,7 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>128.5</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
@@ -1667,7 +1671,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -1732,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1776,17 +1780,17 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -1851,7 +1855,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1905,7 +1909,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1970,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2021,7 +2025,7 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
@@ -2093,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2132,18 +2136,22 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB14" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB14" s="2" t="inlineStr">
+        <is>
+          <t>131.0</t>
+        </is>
+      </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -2208,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2252,17 +2260,17 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>130.5</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -2323,7 +2331,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2374,7 +2382,7 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
@@ -2446,7 +2454,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2490,13 +2498,17 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB17" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr">
+        <is>
+          <t>131.0</t>
+        </is>
+      </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2573,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2605,17 +2617,17 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>129.5</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2692,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2719,7 +2731,7 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -2799,7 +2811,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2853,7 +2865,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -2918,7 +2930,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -3037,7 +3049,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3091,7 +3103,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -3156,7 +3168,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3386,7 +3398,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3559,7 +3571,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -3678,7 +3690,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -3743,7 +3755,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3797,7 +3809,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -3862,7 +3874,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -4035,7 +4047,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -4100,7 +4112,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4154,7 +4166,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -4273,7 +4285,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -4338,7 +4350,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4430,24 +4442,24 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>139分钟</t>
+          <t>137分钟</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr"/>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4457,7 +4469,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4506,12 +4518,12 @@
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -4658,32 +4670,36 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M36" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -4691,7 +4707,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4715,17 +4731,17 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z36" s="2" t="inlineStr">
@@ -4735,13 +4751,17 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB36" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -4779,12 +4799,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>128分钟</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr"/>
@@ -4806,7 +4826,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4855,7 +4875,7 @@
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>128.5</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
@@ -4893,7 +4913,7 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程34%处后消失；随后反向物理轨迹由seq37推进至seq49，推进12站，达到≥2站确认条件</t>
+          <t>原方向在全程34%处后消失；随后反向物理轨迹由seq37推进至seq60，推进23站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -4921,7 +4941,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4976,7 +4996,7 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
@@ -5048,7 +5068,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5102,7 +5122,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -5130,32 +5150,36 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr"/>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M40" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
           <t>06:40</t>
@@ -5163,7 +5187,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5187,17 +5211,17 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z40" s="2" t="inlineStr">
@@ -5207,17 +5231,17 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -5245,32 +5269,36 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr"/>
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M41" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -5278,7 +5306,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5302,17 +5330,17 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z41" s="2" t="inlineStr">
@@ -5322,17 +5350,17 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>130.5</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -5360,32 +5388,36 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr"/>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M42" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -5393,7 +5425,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5417,33 +5449,37 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB42" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB42" s="2" t="inlineStr">
+        <is>
+          <t>131.0</t>
+        </is>
+      </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -5471,32 +5507,36 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr"/>
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M43" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -5504,7 +5544,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5528,17 +5568,17 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y43" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z43" s="2" t="inlineStr">
@@ -5548,17 +5588,17 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>129.5</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -5586,32 +5626,36 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr"/>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -5619,7 +5663,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5643,17 +5687,17 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y44" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z44" s="2" t="inlineStr">
@@ -5663,13 +5707,17 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB44" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB44" s="2" t="inlineStr">
+        <is>
+          <t>131.0</t>
+        </is>
+      </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -5730,7 +5778,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5784,7 +5832,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -5845,7 +5893,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5884,7 +5932,7 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
@@ -5960,7 +6008,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6075,7 +6123,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6129,7 +6177,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -6190,7 +6238,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6305,7 +6353,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6420,7 +6468,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6474,7 +6522,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -6535,7 +6583,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6650,7 +6698,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6765,7 +6813,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6819,7 +6867,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -6880,7 +6928,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6929,7 +6977,7 @@
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>128.5</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
@@ -6942,22 +6990,22 @@
       <c r="A56" s="2" t="inlineStr"/>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>沪A68375D</t>
+          <t>沪A79307D</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="E56" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
@@ -6990,12 +7038,12 @@
       <c r="M56" s="2" t="inlineStr"/>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7009,47 +7057,610 @@
       <c r="T56" s="2" t="inlineStr"/>
       <c r="U56" s="2" t="inlineStr">
         <is>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="V56" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W56" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y56" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z56" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB56" s="2" t="inlineStr"/>
+      <c r="AC56" s="2" t="inlineStr">
+        <is>
+          <t>—/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr"/>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>沪A68375D</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
           <t>12:30</t>
         </is>
       </c>
-      <c r="V56" s="2" t="inlineStr">
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr"/>
+      <c r="K57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr"/>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q57" s="2" t="inlineStr"/>
+      <c r="R57" s="2" t="inlineStr"/>
+      <c r="S57" s="2" t="inlineStr"/>
+      <c r="T57" s="2" t="inlineStr"/>
+      <c r="U57" s="2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="V57" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W56" s="2" t="inlineStr">
+      <c r="W57" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X56" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Y56" s="2" t="inlineStr">
+      <c r="X57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y57" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z56" s="2" t="inlineStr">
+      <c r="Z57" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA56" s="2" t="inlineStr">
+      <c r="AA57" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB56" s="2" t="inlineStr">
-        <is>
-          <t>132.0</t>
-        </is>
-      </c>
-      <c r="AC56" s="2" t="inlineStr">
-        <is>
-          <t>13/29</t>
+      <c r="AB57" s="2" t="inlineStr">
+        <is>
+          <t>131.0</t>
+        </is>
+      </c>
+      <c r="AC57" s="2" t="inlineStr">
+        <is>
+          <t>14/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr"/>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr"/>
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr"/>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q58" s="2" t="inlineStr"/>
+      <c r="R58" s="2" t="inlineStr"/>
+      <c r="S58" s="2" t="inlineStr"/>
+      <c r="T58" s="2" t="inlineStr"/>
+      <c r="U58" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="V58" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W58" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y58" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z58" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB58" s="2" t="inlineStr"/>
+      <c r="AC58" s="2" t="inlineStr">
+        <is>
+          <t>—/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr"/>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>沪A02316D</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr"/>
+      <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr"/>
+      <c r="N59" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q59" s="2" t="inlineStr"/>
+      <c r="R59" s="2" t="inlineStr"/>
+      <c r="S59" s="2" t="inlineStr"/>
+      <c r="T59" s="2" t="inlineStr"/>
+      <c r="U59" s="2" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="V59" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W59" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y59" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z59" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB59" s="2" t="inlineStr">
+        <is>
+          <t>131.0</t>
+        </is>
+      </c>
+      <c r="AC59" s="2" t="inlineStr">
+        <is>
+          <t>14/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr"/>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>沪A37267D</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr"/>
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr"/>
+      <c r="N60" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="inlineStr"/>
+      <c r="R60" s="2" t="inlineStr"/>
+      <c r="S60" s="2" t="inlineStr"/>
+      <c r="T60" s="2" t="inlineStr"/>
+      <c r="U60" s="2" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="V60" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W60" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y60" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z60" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB60" s="2" t="inlineStr"/>
+      <c r="AC60" s="2" t="inlineStr">
+        <is>
+          <t>—/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr"/>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>沪A05218D</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr"/>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr"/>
+      <c r="N61" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q61" s="2" t="inlineStr"/>
+      <c r="R61" s="2" t="inlineStr"/>
+      <c r="S61" s="2" t="inlineStr"/>
+      <c r="T61" s="2" t="inlineStr"/>
+      <c r="U61" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="V61" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W61" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y61" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z61" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB61" s="2" t="inlineStr">
+        <is>
+          <t>123.0</t>
+        </is>
+      </c>
+      <c r="AC61" s="2" t="inlineStr">
+        <is>
+          <t>1/29</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-27-浦东35路.xlsx
+++ b/data/export/2026-09-27-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC61"/>
+  <dimension ref="A1:AC66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>1/29</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1498,7 +1498,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -1909,7 +1909,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -1970,7 +1970,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2270,7 +2270,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -2331,7 +2331,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2454,7 +2454,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2612,14 +2612,14 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA18" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
           <t>129.5</t>
@@ -2627,7 +2627,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>123.0</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>1/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -2811,7 +2811,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2855,17 +2855,17 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>136.5</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -2930,7 +2930,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2969,22 +2969,22 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA21" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>130.5</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -3049,7 +3049,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3093,17 +3093,17 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -3168,7 +3168,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3207,12 +3207,12 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="AA23" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3442,17 +3442,17 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -3755,7 +3755,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="AA28" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3913,7 +3913,7 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
@@ -3928,7 +3928,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -4112,7 +4112,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4350,7 +4350,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4404,7 +4404,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>1/29</t>
         </is>
       </c>
     </row>
@@ -4469,7 +4469,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4880,7 +4880,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -4941,7 +4941,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5122,7 +5122,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -5360,7 +5360,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -5425,7 +5425,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5544,7 +5544,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5583,14 +5583,14 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA43" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
           <t>129.5</t>
@@ -5598,7 +5598,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -5648,12 +5648,12 @@
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5663,7 +5663,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5745,32 +5745,36 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>137分钟</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr"/>
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M45" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -5778,7 +5782,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5802,17 +5806,17 @@
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z45" s="2" t="inlineStr">
@@ -5822,17 +5826,17 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>136.5</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -5860,32 +5864,36 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>137分钟</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr"/>
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M46" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
           <t>06:40</t>
@@ -5893,7 +5901,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5917,17 +5925,17 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y46" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z46" s="2" t="inlineStr">
@@ -5937,17 +5945,17 @@
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>123.0</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>1/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -5975,32 +5983,36 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr"/>
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M47" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
           <t>07:31</t>
@@ -6008,7 +6020,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6032,37 +6044,37 @@
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y47" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA47" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>130.5</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -6090,32 +6102,36 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr"/>
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M48" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -6123,7 +6139,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6147,17 +6163,17 @@
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y48" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z48" s="2" t="inlineStr">
@@ -6167,17 +6183,17 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -6205,32 +6221,36 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr"/>
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M49" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
           <t>06:40</t>
@@ -6238,7 +6258,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6262,27 +6282,27 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y49" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="AA49" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
@@ -6320,32 +6340,36 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>122分钟</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr"/>
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M50" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -6353,7 +6377,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6377,17 +6401,17 @@
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y50" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z50" s="2" t="inlineStr">
@@ -6397,17 +6421,17 @@
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -6435,32 +6459,36 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>136分钟</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M51" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6468,7 +6496,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6492,27 +6520,27 @@
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y51" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="AA51" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
@@ -6583,7 +6611,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6622,7 +6650,7 @@
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA52" s="2" t="inlineStr">
@@ -6637,7 +6665,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -6698,7 +6726,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6752,7 +6780,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>1/29</t>
         </is>
       </c>
     </row>
@@ -6813,7 +6841,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6928,7 +6956,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6982,7 +7010,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -7043,7 +7071,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7154,7 +7182,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7269,7 +7297,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7380,7 +7408,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7495,7 +7523,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7606,7 +7634,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7650,17 +7678,592 @@
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>123.0</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>1/29</t>
+          <t>10/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr"/>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>沪A95621D</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr"/>
+      <c r="K62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr"/>
+      <c r="N62" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q62" s="2" t="inlineStr"/>
+      <c r="R62" s="2" t="inlineStr"/>
+      <c r="S62" s="2" t="inlineStr"/>
+      <c r="T62" s="2" t="inlineStr"/>
+      <c r="U62" s="2" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="V62" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W62" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y62" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z62" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB62" s="2" t="inlineStr">
+        <is>
+          <t>129.5</t>
+        </is>
+      </c>
+      <c r="AC62" s="2" t="inlineStr">
+        <is>
+          <t>8/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr"/>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>沪A36993D</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr"/>
+      <c r="K63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr"/>
+      <c r="N63" s="2" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q63" s="2" t="inlineStr"/>
+      <c r="R63" s="2" t="inlineStr"/>
+      <c r="S63" s="2" t="inlineStr"/>
+      <c r="T63" s="2" t="inlineStr"/>
+      <c r="U63" s="2" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="V63" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W63" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y63" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z63" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB63" s="2" t="inlineStr">
+        <is>
+          <t>130.5</t>
+        </is>
+      </c>
+      <c r="AC63" s="2" t="inlineStr">
+        <is>
+          <t>12/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr"/>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>沪A51682D</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr"/>
+      <c r="K64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr"/>
+      <c r="N64" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q64" s="2" t="inlineStr"/>
+      <c r="R64" s="2" t="inlineStr"/>
+      <c r="S64" s="2" t="inlineStr"/>
+      <c r="T64" s="2" t="inlineStr"/>
+      <c r="U64" s="2" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="V64" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W64" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y64" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z64" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA64" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB64" s="2" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="AC64" s="2" t="inlineStr">
+        <is>
+          <t>3/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr"/>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>沪A15330A</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr"/>
+      <c r="K65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr"/>
+      <c r="N65" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q65" s="2" t="inlineStr"/>
+      <c r="R65" s="2" t="inlineStr"/>
+      <c r="S65" s="2" t="inlineStr"/>
+      <c r="T65" s="2" t="inlineStr"/>
+      <c r="U65" s="2" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="V65" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W65" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y65" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z65" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB65" s="2" t="inlineStr">
+        <is>
+          <t>129.5</t>
+        </is>
+      </c>
+      <c r="AC65" s="2" t="inlineStr">
+        <is>
+          <t>8/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr"/>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>沪A62880D</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr"/>
+      <c r="K66" s="2" t="inlineStr"/>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr"/>
+      <c r="N66" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q66" s="2" t="inlineStr"/>
+      <c r="R66" s="2" t="inlineStr"/>
+      <c r="S66" s="2" t="inlineStr"/>
+      <c r="T66" s="2" t="inlineStr"/>
+      <c r="U66" s="2" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="V66" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W66" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y66" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z66" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB66" s="2" t="inlineStr">
+        <is>
+          <t>136.0</t>
+        </is>
+      </c>
+      <c r="AC66" s="2" t="inlineStr">
+        <is>
+          <t>22/29</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-27-浦东35路.xlsx
+++ b/data/export/2026-09-27-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC66"/>
+  <dimension ref="A1:AC72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -713,17 +713,17 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>129.5</t>
+          <t>128.7</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,14 +827,14 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
           <t>132.5</t>
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>25/29</t>
+          <t>26/29</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,17 +1065,17 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>121.3</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1379,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
@@ -1498,7 +1498,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1537,22 +1537,22 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA9" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>130.7</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -1909,7 +1909,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -1970,7 +1970,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2025,18 +2025,22 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB13" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr">
+        <is>
+          <t>136.0</t>
+        </is>
+      </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2101,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2270,7 +2274,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -2331,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2573,7 +2577,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2692,7 +2696,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2746,7 +2750,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -2930,7 +2934,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2984,7 +2988,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -3168,7 +3172,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3517,7 +3521,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3556,7 +3560,7 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
@@ -3690,7 +3694,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -3755,7 +3759,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3804,12 +3808,12 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>136.5</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -3874,7 +3878,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3918,17 +3922,17 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>129.5</t>
+          <t>128.7</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -3993,7 +3997,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4032,14 +4036,14 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA30" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
           <t>132.5</t>
@@ -4047,7 +4051,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -4112,7 +4116,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4156,17 +4160,17 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -4285,7 +4289,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>25/29</t>
+          <t>26/29</t>
         </is>
       </c>
     </row>
@@ -4350,7 +4354,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4389,17 +4393,17 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA33" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>121.3</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
@@ -4469,7 +4473,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4588,7 +4592,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4627,7 +4631,7 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
@@ -4826,7 +4830,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4865,22 +4869,22 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA37" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>130.7</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -4941,7 +4945,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5122,7 +5126,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -5360,7 +5364,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -5425,7 +5429,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5544,7 +5548,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5901,7 +5905,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5955,7 +5959,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -6020,7 +6024,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6074,7 +6078,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -6258,7 +6262,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6469,24 +6473,24 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>136分钟</t>
+          <t>137分钟</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -6496,7 +6500,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6545,12 +6549,12 @@
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>136.5</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -6578,32 +6582,36 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M52" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6611,7 +6619,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6635,17 +6643,17 @@
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y52" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z52" s="2" t="inlineStr">
@@ -6655,17 +6663,17 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>129.5</t>
+          <t>128.7</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -6693,32 +6701,36 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>116分钟</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr"/>
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M53" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6726,7 +6738,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6750,32 +6762,32 @@
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y53" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA53" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>121.3</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
@@ -6808,32 +6820,36 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M54" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
           <t>06:40</t>
@@ -6841,7 +6857,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6865,17 +6881,17 @@
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y54" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z54" s="2" t="inlineStr">
@@ -6885,17 +6901,17 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -6923,32 +6939,36 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>134分钟</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr"/>
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M55" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -6956,7 +6976,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6980,37 +7000,37 @@
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y55" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA55" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>130.7</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -7038,12 +7058,12 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程38%处后消失；随后反向物理轨迹由seq37推进至seq55，推进18站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -7071,18 +7091,34 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr">
+        <is>
+          <t>沪南路高科西路</t>
+        </is>
+      </c>
+      <c r="R56" s="2" t="inlineStr">
+        <is>
           <t>13:20</t>
         </is>
       </c>
-      <c r="P56" s="2" t="inlineStr">
-        <is>
-          <t>SHMAAS</t>
-        </is>
-      </c>
-      <c r="Q56" s="2" t="inlineStr"/>
-      <c r="R56" s="2" t="inlineStr"/>
-      <c r="S56" s="2" t="inlineStr"/>
-      <c r="T56" s="2" t="inlineStr"/>
+      <c r="S56" s="2" t="inlineStr">
+        <is>
+          <t>13:26</t>
+        </is>
+      </c>
+      <c r="T56" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq25映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±5分钟；反向位置浦建路锦绣路 ETA 10分钟参与校验</t>
+        </is>
+      </c>
       <c r="U56" s="2" t="inlineStr">
         <is>
           <t>12:28</t>
@@ -7182,7 +7218,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7264,32 +7300,36 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>136分钟</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr"/>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M58" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -7297,7 +7337,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7321,33 +7361,37 @@
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y58" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB58" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB58" s="2" t="inlineStr">
+        <is>
+          <t>136.0</t>
+        </is>
+      </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -7408,7 +7452,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7523,7 +7567,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7634,7 +7678,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7688,7 +7732,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -7749,7 +7793,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7864,7 +7908,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7918,7 +7962,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -7979,7 +8023,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8094,7 +8138,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8138,17 +8182,17 @@
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>129.5</t>
+          <t>128.7</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -8209,7 +8253,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8258,12 +8302,702 @@
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
+          <t>136.5</t>
+        </is>
+      </c>
+      <c r="AC66" s="2" t="inlineStr">
+        <is>
+          <t>24/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr"/>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr"/>
+      <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr"/>
+      <c r="N67" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="P67" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q67" s="2" t="inlineStr"/>
+      <c r="R67" s="2" t="inlineStr"/>
+      <c r="S67" s="2" t="inlineStr"/>
+      <c r="T67" s="2" t="inlineStr"/>
+      <c r="U67" s="2" t="inlineStr">
+        <is>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="V67" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W67" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y67" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z67" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB67" s="2" t="inlineStr">
+        <is>
+          <t>132.0</t>
+        </is>
+      </c>
+      <c r="AC67" s="2" t="inlineStr">
+        <is>
+          <t>17/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr"/>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>沪A65668D</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr"/>
+      <c r="K68" s="2" t="inlineStr"/>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr"/>
+      <c r="N68" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q68" s="2" t="inlineStr"/>
+      <c r="R68" s="2" t="inlineStr"/>
+      <c r="S68" s="2" t="inlineStr"/>
+      <c r="T68" s="2" t="inlineStr"/>
+      <c r="U68" s="2" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="V68" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W68" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y68" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z68" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB68" s="2" t="inlineStr">
+        <is>
+          <t>121.3</t>
+        </is>
+      </c>
+      <c r="AC68" s="2" t="inlineStr">
+        <is>
+          <t>1/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr"/>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>沪A02891D</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr"/>
+      <c r="K69" s="2" t="inlineStr"/>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr"/>
+      <c r="N69" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="P69" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q69" s="2" t="inlineStr"/>
+      <c r="R69" s="2" t="inlineStr"/>
+      <c r="S69" s="2" t="inlineStr"/>
+      <c r="T69" s="2" t="inlineStr"/>
+      <c r="U69" s="2" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="V69" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W69" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y69" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z69" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA69" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB69" s="2" t="inlineStr">
+        <is>
+          <t>132.5</t>
+        </is>
+      </c>
+      <c r="AC69" s="2" t="inlineStr">
+        <is>
+          <t>20/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr"/>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>沪A66883D</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr"/>
+      <c r="K70" s="2" t="inlineStr"/>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr"/>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q70" s="2" t="inlineStr"/>
+      <c r="R70" s="2" t="inlineStr"/>
+      <c r="S70" s="2" t="inlineStr"/>
+      <c r="T70" s="2" t="inlineStr"/>
+      <c r="U70" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="V70" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W70" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y70" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z70" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB70" s="2" t="inlineStr">
+        <is>
+          <t>130.7</t>
+        </is>
+      </c>
+      <c r="AC70" s="2" t="inlineStr">
+        <is>
+          <t>13/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr"/>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>沪A90275D</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr"/>
+      <c r="K71" s="2" t="inlineStr"/>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr"/>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="P71" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q71" s="2" t="inlineStr"/>
+      <c r="R71" s="2" t="inlineStr"/>
+      <c r="S71" s="2" t="inlineStr"/>
+      <c r="T71" s="2" t="inlineStr"/>
+      <c r="U71" s="2" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="V71" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W71" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y71" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z71" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB71" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
+      <c r="AC71" s="2" t="inlineStr">
+        <is>
+          <t>4/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr"/>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr"/>
+      <c r="K72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr"/>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q72" s="2" t="inlineStr"/>
+      <c r="R72" s="2" t="inlineStr"/>
+      <c r="S72" s="2" t="inlineStr"/>
+      <c r="T72" s="2" t="inlineStr"/>
+      <c r="U72" s="2" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="V72" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W72" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y72" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z72" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB72" s="2" t="inlineStr">
+        <is>
           <t>136.0</t>
         </is>
       </c>
-      <c r="AC66" s="2" t="inlineStr">
-        <is>
-          <t>22/29</t>
+      <c r="AC72" s="2" t="inlineStr">
+        <is>
+          <t>23/29</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-27-浦东35路.xlsx
+++ b/data/export/2026-09-27-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC72"/>
+  <dimension ref="A1:AC73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1189,17 +1189,17 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>132.3</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1498,7 +1498,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1790,7 +1790,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -1970,7 +1970,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2101,7 +2101,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2335,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2577,7 +2577,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2696,7 +2696,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -3172,7 +3172,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3521,7 +3521,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3575,7 +3575,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -3759,7 +3759,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3878,7 +3878,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3997,7 +3997,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4170,7 +4170,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -4354,7 +4354,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4473,7 +4473,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4517,17 +4517,17 @@
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>132.3</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -4592,7 +4592,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4830,7 +4830,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4945,7 +4945,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5000,7 +5000,7 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
@@ -5245,7 +5245,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -5429,7 +5429,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5548,7 +5548,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5905,7 +5905,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -6024,7 +6024,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6262,7 +6262,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6500,7 +6500,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6619,7 +6619,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6738,7 +6738,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6911,7 +6911,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -6976,7 +6976,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7063,7 +7063,7 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程38%处后消失；随后反向物理轨迹由seq37推进至seq55，推进18站，达到≥2站确认条件</t>
+          <t>原方向在全程38%处后消失；随后反向物理轨迹由seq37推进至seq62，推进25站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -7091,7 +7091,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7146,7 +7146,7 @@
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA56" s="2" t="inlineStr">
@@ -7185,32 +7185,36 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>135分钟</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr"/>
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M57" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -7218,7 +7222,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7242,17 +7246,17 @@
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y57" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z57" s="2" t="inlineStr">
@@ -7262,17 +7266,17 @@
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>132.3</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -7337,7 +7341,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7452,7 +7456,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7567,7 +7571,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7678,7 +7682,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7793,7 +7797,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7908,7 +7912,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -8023,7 +8027,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8138,7 +8142,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8253,7 +8257,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8368,7 +8372,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8422,7 +8426,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -8483,7 +8487,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8598,7 +8602,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8713,7 +8717,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8828,7 +8832,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8890,22 +8894,22 @@
       <c r="A72" s="2" t="inlineStr"/>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>沪A37823D</t>
+          <t>沪A79307D</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
-        <is>
-          <t>15:25</t>
-        </is>
-      </c>
-      <c r="E72" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
@@ -8938,12 +8942,12 @@
       <c r="M72" s="2" t="inlineStr"/>
       <c r="N72" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -8957,45 +8961,156 @@
       <c r="T72" s="2" t="inlineStr"/>
       <c r="U72" s="2" t="inlineStr">
         <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="V72" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W72" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y72" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z72" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB72" s="2" t="inlineStr"/>
+      <c r="AC72" s="2" t="inlineStr">
+        <is>
+          <t>—/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr"/>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
           <t>15:25</t>
         </is>
       </c>
-      <c r="V72" s="2" t="inlineStr">
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr"/>
+      <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr"/>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>14:31</t>
+        </is>
+      </c>
+      <c r="P73" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q73" s="2" t="inlineStr"/>
+      <c r="R73" s="2" t="inlineStr"/>
+      <c r="S73" s="2" t="inlineStr"/>
+      <c r="T73" s="2" t="inlineStr"/>
+      <c r="U73" s="2" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="V73" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W72" s="2" t="inlineStr">
+      <c r="W73" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X72" s="2" t="inlineStr">
+      <c r="X73" s="2" t="inlineStr">
         <is>
           <t>待确认</t>
         </is>
       </c>
-      <c r="Y72" s="2" t="inlineStr">
+      <c r="Y73" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z72" s="2" t="inlineStr">
+      <c r="Z73" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA72" s="2" t="inlineStr">
+      <c r="AA73" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB72" s="2" t="inlineStr">
+      <c r="AB73" s="2" t="inlineStr">
         <is>
           <t>136.0</t>
         </is>
       </c>
-      <c r="AC72" s="2" t="inlineStr">
+      <c r="AC73" s="2" t="inlineStr">
         <is>
           <t>23/29</t>
         </is>

--- a/data/export/2026-09-27-浦东35路.xlsx
+++ b/data/export/2026-09-27-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC73"/>
+  <dimension ref="A1:AC77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1194,12 +1194,12 @@
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>132.3</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -1314,7 +1314,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -1855,7 +1855,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
@@ -1909,7 +1909,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -1970,7 +1970,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2035,12 +2035,12 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>27/29</t>
         </is>
       </c>
     </row>
@@ -2101,7 +2101,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2145,17 +2145,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -2220,7 +2220,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2259,14 +2259,14 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA15" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
           <t>130.5</t>
@@ -2274,7 +2274,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -2335,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2386,18 +2386,22 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB16" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2516,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -2577,7 +2581,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2621,17 +2625,17 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>129.5</t>
+          <t>129.7</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -2696,7 +2700,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2740,17 +2744,17 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>127.7</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -2934,7 +2938,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2988,7 +2992,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -3107,7 +3111,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -3172,7 +3176,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3226,7 +3230,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -3521,7 +3525,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3640,7 +3644,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3679,14 +3683,14 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA27" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
           <t>133.0</t>
@@ -3694,7 +3698,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -3759,7 +3763,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3878,7 +3882,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3932,7 +3936,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -3997,7 +4001,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4051,7 +4055,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -4354,7 +4358,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4473,7 +4477,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4522,12 +4526,12 @@
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>132.3</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -4592,7 +4596,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4646,7 +4650,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -4765,7 +4769,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -4830,7 +4834,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4884,7 +4888,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -4945,7 +4949,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5072,7 +5076,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5111,7 +5115,7 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
@@ -5126,7 +5130,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -5310,7 +5314,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5349,14 +5353,14 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA41" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
           <t>130.5</t>
@@ -5364,7 +5368,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -5429,7 +5433,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5473,17 +5477,17 @@
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -5548,7 +5552,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5592,17 +5596,17 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>129.5</t>
+          <t>129.7</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -5721,7 +5725,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -5905,7 +5909,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5949,17 +5953,17 @@
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>127.7</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -6024,7 +6028,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6078,7 +6082,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -6197,7 +6201,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -6262,7 +6266,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6316,7 +6320,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -6500,7 +6504,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6619,7 +6623,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6673,7 +6677,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -6738,7 +6742,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6976,7 +6980,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7030,7 +7034,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -7091,7 +7095,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7195,24 +7199,24 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>135分钟</t>
+          <t>137分钟</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr"/>
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -7222,7 +7226,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7271,12 +7275,12 @@
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>132.3</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -7314,24 +7318,24 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>136分钟</t>
+          <t>140分钟</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr"/>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -7341,7 +7345,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7390,12 +7394,12 @@
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>27/29</t>
         </is>
       </c>
     </row>
@@ -7423,32 +7427,36 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>137分钟</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr"/>
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M59" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -7456,7 +7464,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7480,17 +7488,17 @@
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y59" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z59" s="2" t="inlineStr">
@@ -7500,17 +7508,17 @@
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -7538,32 +7546,36 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr"/>
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M60" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -7571,7 +7583,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7595,33 +7607,37 @@
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y60" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB60" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB60" s="2" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -7649,32 +7665,36 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>123分钟</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr"/>
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M61" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
           <t>06:40</t>
@@ -7682,7 +7702,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7706,17 +7726,17 @@
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y61" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z61" s="2" t="inlineStr">
@@ -7726,17 +7746,17 @@
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>127.7</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -7764,32 +7784,36 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr"/>
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M62" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -7797,7 +7821,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7821,17 +7845,17 @@
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y62" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z62" s="2" t="inlineStr">
@@ -7841,17 +7865,17 @@
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>129.5</t>
+          <t>129.7</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -7912,7 +7936,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7966,7 +7990,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -8027,7 +8051,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8081,7 +8105,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -8142,7 +8166,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8196,7 +8220,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -8257,7 +8281,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8372,7 +8396,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8487,7 +8511,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8602,7 +8626,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8656,7 +8680,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -8717,7 +8741,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8771,7 +8795,7 @@
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -8832,7 +8856,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8886,7 +8910,7 @@
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -8947,7 +8971,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9058,7 +9082,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9107,12 +9131,472 @@
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>27/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr"/>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>沪A71572D</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr"/>
+      <c r="K74" s="2" t="inlineStr"/>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr"/>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q74" s="2" t="inlineStr"/>
+      <c r="R74" s="2" t="inlineStr"/>
+      <c r="S74" s="2" t="inlineStr"/>
+      <c r="T74" s="2" t="inlineStr"/>
+      <c r="U74" s="2" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="V74" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W74" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y74" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z74" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB74" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
+      <c r="AC74" s="2" t="inlineStr">
+        <is>
+          <t>11/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr"/>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>沪A67672D</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr"/>
+      <c r="K75" s="2" t="inlineStr"/>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr"/>
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="P75" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q75" s="2" t="inlineStr"/>
+      <c r="R75" s="2" t="inlineStr"/>
+      <c r="S75" s="2" t="inlineStr"/>
+      <c r="T75" s="2" t="inlineStr"/>
+      <c r="U75" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="V75" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W75" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y75" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z75" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB75" s="2" t="inlineStr">
+        <is>
+          <t>133.0</t>
+        </is>
+      </c>
+      <c r="AC75" s="2" t="inlineStr">
+        <is>
+          <t>20/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr"/>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>沪A70597D</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr"/>
+      <c r="K76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr"/>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="P76" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q76" s="2" t="inlineStr"/>
+      <c r="R76" s="2" t="inlineStr"/>
+      <c r="S76" s="2" t="inlineStr"/>
+      <c r="T76" s="2" t="inlineStr"/>
+      <c r="U76" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="V76" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W76" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y76" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z76" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA76" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB76" s="2" t="inlineStr">
+        <is>
+          <t>130.5</t>
+        </is>
+      </c>
+      <c r="AC76" s="2" t="inlineStr">
+        <is>
+          <t>12/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr"/>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>沪A37267D</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>16:05</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr"/>
+      <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr"/>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="P77" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q77" s="2" t="inlineStr"/>
+      <c r="R77" s="2" t="inlineStr"/>
+      <c r="S77" s="2" t="inlineStr"/>
+      <c r="T77" s="2" t="inlineStr"/>
+      <c r="U77" s="2" t="inlineStr">
+        <is>
+          <t>16:05</t>
+        </is>
+      </c>
+      <c r="V77" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W77" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y77" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z77" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA77" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB77" s="2" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
+      <c r="AC77" s="2" t="inlineStr">
+        <is>
+          <t>2/29</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-27-浦东35路.xlsx
+++ b/data/export/2026-09-27-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC77"/>
+  <dimension ref="A1:AC83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -713,12 +713,12 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>128.7</t>
+          <t>128.2</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,7 +946,7 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1070,12 +1070,12 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>121.3</t>
+          <t>121.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
@@ -1260,7 +1260,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1299,7 +1299,7 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
@@ -1379,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1498,7 +1498,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1775,14 +1775,14 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
           <t>132.0</t>
@@ -1790,7 +1790,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -1855,7 +1855,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1970,7 +1970,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2155,7 +2155,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -2220,7 +2220,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2335,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2581,7 +2581,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2630,7 +2630,7 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>129.7</t>
+          <t>128.7</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
@@ -2819,7 +2819,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2858,14 +2858,14 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA20" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
           <t>136.5</t>
@@ -2873,7 +2873,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -2938,7 +2938,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2982,17 +2982,17 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>130.5</t>
+          <t>130.7</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -3176,7 +3176,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>126.7</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
@@ -3406,7 +3406,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3445,7 +3445,7 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
@@ -3525,7 +3525,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3569,12 +3569,12 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>131.5</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
@@ -3644,7 +3644,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3763,7 +3763,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3807,17 +3807,17 @@
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>136.5</t>
+          <t>133.7</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -3882,7 +3882,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3926,12 +3926,12 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>128.7</t>
+          <t>128.2</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
@@ -4001,7 +4001,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4120,7 +4120,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4159,14 +4159,14 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA31" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
           <t>132.0</t>
@@ -4174,7 +4174,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -4239,7 +4239,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4278,7 +4278,7 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
@@ -4358,7 +4358,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4402,12 +4402,12 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>121.3</t>
+          <t>121.0</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4715,7 +4715,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4754,7 +4754,7 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
@@ -4834,7 +4834,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4888,7 +4888,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -4949,7 +4949,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5195,7 +5195,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5234,14 +5234,14 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA40" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
           <t>132.0</t>
@@ -5249,7 +5249,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -5314,7 +5314,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5487,7 +5487,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -5552,7 +5552,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5601,7 +5601,7 @@
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>129.7</t>
+          <t>128.7</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
@@ -5790,7 +5790,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5829,14 +5829,14 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA45" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
           <t>136.5</t>
@@ -5844,7 +5844,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -6028,7 +6028,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6072,17 +6072,17 @@
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>130.5</t>
+          <t>130.7</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -6266,7 +6266,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6310,12 +6310,12 @@
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>126.7</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
@@ -6385,7 +6385,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6424,7 +6424,7 @@
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA50" s="2" t="inlineStr">
@@ -6504,7 +6504,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6548,17 +6548,17 @@
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>136.5</t>
+          <t>133.7</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -6623,7 +6623,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6667,12 +6667,12 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>128.7</t>
+          <t>128.2</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
@@ -6742,7 +6742,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6786,12 +6786,12 @@
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>121.3</t>
+          <t>121.0</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
@@ -6861,7 +6861,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6900,14 +6900,14 @@
       </c>
       <c r="Z54" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA54" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
           <t>132.0</t>
@@ -6915,7 +6915,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -6980,7 +6980,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7034,7 +7034,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -7095,7 +7095,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7345,7 +7345,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7518,7 +7518,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -7583,7 +7583,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7794,24 +7794,24 @@
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>130分钟</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr"/>
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -7821,7 +7821,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7870,7 +7870,7 @@
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>129.7</t>
+          <t>128.7</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
@@ -7903,32 +7903,36 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr"/>
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M63" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
           <t>07:31</t>
@@ -7936,7 +7940,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7960,17 +7964,17 @@
       </c>
       <c r="W63" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y63" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z63" s="2" t="inlineStr">
@@ -7980,17 +7984,17 @@
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>130.5</t>
+          <t>130.7</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -8018,32 +8022,36 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr"/>
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M64" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
           <t>06:40</t>
@@ -8051,7 +8059,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8075,17 +8083,17 @@
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y64" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z64" s="2" t="inlineStr">
@@ -8095,12 +8103,12 @@
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>126.7</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
@@ -8133,32 +8141,36 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr"/>
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M65" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8166,7 +8178,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8190,17 +8202,17 @@
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y65" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z65" s="2" t="inlineStr">
@@ -8210,12 +8222,12 @@
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>128.7</t>
+          <t>128.2</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
@@ -8248,32 +8260,36 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr"/>
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M66" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8281,7 +8297,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8305,17 +8321,17 @@
       </c>
       <c r="W66" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y66" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z66" s="2" t="inlineStr">
@@ -8325,17 +8341,17 @@
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>136.5</t>
+          <t>133.7</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -8363,32 +8379,36 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr"/>
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M67" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8396,7 +8416,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8420,17 +8440,17 @@
       </c>
       <c r="W67" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y67" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z67" s="2" t="inlineStr">
@@ -8440,12 +8460,12 @@
       </c>
       <c r="AA67" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>131.5</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
@@ -8478,32 +8498,36 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>120分钟</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr"/>
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M68" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8511,7 +8535,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8535,17 +8559,17 @@
       </c>
       <c r="W68" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y68" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z68" s="2" t="inlineStr">
@@ -8555,12 +8579,12 @@
       </c>
       <c r="AA68" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>121.3</t>
+          <t>121.0</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
@@ -8626,7 +8650,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8741,7 +8765,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8795,7 +8819,7 @@
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -8856,7 +8880,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8971,7 +8995,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9082,7 +9106,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9197,7 +9221,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9312,7 +9336,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9427,7 +9451,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9542,7 +9566,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9600,6 +9624,696 @@
         </is>
       </c>
     </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr"/>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>沪A73927D</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr"/>
+      <c r="K78" s="2" t="inlineStr"/>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr"/>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q78" s="2" t="inlineStr"/>
+      <c r="R78" s="2" t="inlineStr"/>
+      <c r="S78" s="2" t="inlineStr"/>
+      <c r="T78" s="2" t="inlineStr"/>
+      <c r="U78" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="V78" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W78" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y78" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z78" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA78" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB78" s="2" t="inlineStr">
+        <is>
+          <t>136.5</t>
+        </is>
+      </c>
+      <c r="AC78" s="2" t="inlineStr">
+        <is>
+          <t>25/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr"/>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>沪A62981D</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr"/>
+      <c r="K79" s="2" t="inlineStr"/>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr"/>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P79" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q79" s="2" t="inlineStr"/>
+      <c r="R79" s="2" t="inlineStr"/>
+      <c r="S79" s="2" t="inlineStr"/>
+      <c r="T79" s="2" t="inlineStr"/>
+      <c r="U79" s="2" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="V79" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W79" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y79" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z79" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA79" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB79" s="2" t="inlineStr">
+        <is>
+          <t>138.0</t>
+        </is>
+      </c>
+      <c r="AC79" s="2" t="inlineStr">
+        <is>
+          <t>26/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr"/>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>沪A15790A</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr"/>
+      <c r="K80" s="2" t="inlineStr"/>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr"/>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P80" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q80" s="2" t="inlineStr"/>
+      <c r="R80" s="2" t="inlineStr"/>
+      <c r="S80" s="2" t="inlineStr"/>
+      <c r="T80" s="2" t="inlineStr"/>
+      <c r="U80" s="2" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="V80" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W80" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y80" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z80" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA80" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB80" s="2" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
+      <c r="AC80" s="2" t="inlineStr">
+        <is>
+          <t>2/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr"/>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>沪A62217D</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr"/>
+      <c r="K81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr"/>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P81" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q81" s="2" t="inlineStr"/>
+      <c r="R81" s="2" t="inlineStr"/>
+      <c r="S81" s="2" t="inlineStr"/>
+      <c r="T81" s="2" t="inlineStr"/>
+      <c r="U81" s="2" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="V81" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W81" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y81" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z81" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA81" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB81" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
+      <c r="AC81" s="2" t="inlineStr">
+        <is>
+          <t>7/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr"/>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>沪A11062A</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr"/>
+      <c r="K82" s="2" t="inlineStr"/>
+      <c r="L82" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr"/>
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P82" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q82" s="2" t="inlineStr"/>
+      <c r="R82" s="2" t="inlineStr"/>
+      <c r="S82" s="2" t="inlineStr"/>
+      <c r="T82" s="2" t="inlineStr"/>
+      <c r="U82" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="V82" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W82" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y82" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z82" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA82" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB82" s="2" t="inlineStr">
+        <is>
+          <t>132.0</t>
+        </is>
+      </c>
+      <c r="AC82" s="2" t="inlineStr">
+        <is>
+          <t>17/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr"/>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>沪A67712D</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr"/>
+      <c r="K83" s="2" t="inlineStr"/>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr"/>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P83" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q83" s="2" t="inlineStr"/>
+      <c r="R83" s="2" t="inlineStr"/>
+      <c r="S83" s="2" t="inlineStr"/>
+      <c r="T83" s="2" t="inlineStr"/>
+      <c r="U83" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="V83" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W83" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y83" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z83" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA83" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB83" s="2" t="inlineStr">
+        <is>
+          <t>132.0</t>
+        </is>
+      </c>
+      <c r="AC83" s="2" t="inlineStr">
+        <is>
+          <t>17/29</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-09-27-浦东35路.xlsx
+++ b/data/export/2026-09-27-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC83"/>
+  <dimension ref="A1:AC91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,17 +827,17 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>132.5</t>
+          <t>132.3</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1075,7 +1075,7 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>121.0</t>
+          <t>121.2</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1260,7 +1260,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1379,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1418,17 +1418,17 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>127.3</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
@@ -1498,7 +1498,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1542,17 +1542,17 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>130.7</t>
+          <t>131.2</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1790,7 +1790,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -1855,7 +1855,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1970,7 +1970,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2025,7 +2025,7 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
@@ -2101,7 +2101,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2140,7 +2140,7 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2220,7 +2220,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2335,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2462,7 +2462,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -2700,7 +2700,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2739,7 +2739,7 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -2819,7 +2819,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -3406,7 +3406,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3525,7 +3525,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3564,17 +3564,17 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA26" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>131.5</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
@@ -3644,7 +3644,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -4001,7 +4001,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4040,17 +4040,17 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA30" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>132.5</t>
+          <t>132.3</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
@@ -4120,7 +4120,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4174,7 +4174,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -4239,7 +4239,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4358,7 +4358,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4407,7 +4407,7 @@
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>121.0</t>
+          <t>121.2</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
@@ -4477,7 +4477,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4516,7 +4516,7 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4635,17 +4635,17 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA35" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>127.3</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
@@ -4715,7 +4715,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4834,7 +4834,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4878,17 +4878,17 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>130.7</t>
+          <t>131.2</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -4949,7 +4949,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5195,7 +5195,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5249,7 +5249,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -5314,7 +5314,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5433,7 +5433,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5472,7 +5472,7 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
@@ -5671,7 +5671,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5710,7 +5710,7 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA44" s="2" t="inlineStr">
@@ -5725,7 +5725,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -5790,7 +5790,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5909,7 +5909,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5948,7 +5948,7 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
@@ -6385,7 +6385,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6742,7 +6742,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6791,7 +6791,7 @@
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>121.0</t>
+          <t>121.2</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
@@ -6861,7 +6861,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6915,7 +6915,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -6980,7 +6980,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7024,17 +7024,17 @@
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>130.7</t>
+          <t>131.2</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -7095,7 +7095,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7226,7 +7226,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7265,7 +7265,7 @@
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA57" s="2" t="inlineStr">
@@ -7345,7 +7345,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7384,7 +7384,7 @@
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA58" s="2" t="inlineStr">
@@ -7464,7 +7464,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7503,7 +7503,7 @@
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA59" s="2" t="inlineStr">
@@ -7583,7 +7583,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7702,7 +7702,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7741,7 +7741,7 @@
       </c>
       <c r="Z61" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA61" s="2" t="inlineStr">
@@ -8389,24 +8389,24 @@
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>131分钟</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr"/>
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
@@ -8416,7 +8416,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8455,17 +8455,17 @@
       </c>
       <c r="Z67" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA67" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>131.5</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
@@ -8508,24 +8508,24 @@
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>120分钟</t>
+          <t>121分钟</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr"/>
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -8535,7 +8535,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8584,7 +8584,7 @@
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>121.0</t>
+          <t>121.2</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
@@ -8617,32 +8617,36 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr"/>
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M69" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8650,7 +8654,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8674,32 +8678,32 @@
       </c>
       <c r="W69" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y69" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z69" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA69" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA69" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>132.5</t>
+          <t>132.3</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
@@ -8732,32 +8736,36 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr"/>
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M70" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -8765,7 +8773,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8789,17 +8797,17 @@
       </c>
       <c r="W70" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y70" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z70" s="2" t="inlineStr">
@@ -8809,17 +8817,17 @@
       </c>
       <c r="AA70" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>130.7</t>
+          <t>131.2</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -8847,32 +8855,36 @@
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr"/>
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M71" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8880,7 +8892,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8904,32 +8916,32 @@
       </c>
       <c r="W71" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y71" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z71" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA71" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>127.3</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
@@ -8962,12 +8974,12 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程34%处后消失；随后反向物理轨迹由seq38推进至seq59，推进21站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
@@ -8995,7 +9007,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9003,10 +9015,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q72" s="2" t="inlineStr"/>
-      <c r="R72" s="2" t="inlineStr"/>
-      <c r="S72" s="2" t="inlineStr"/>
-      <c r="T72" s="2" t="inlineStr"/>
+      <c r="Q72" s="2" t="inlineStr">
+        <is>
+          <t>物理seq23（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R72" s="2" t="inlineStr">
+        <is>
+          <t>16:18</t>
+        </is>
+      </c>
+      <c r="S72" s="2" t="inlineStr">
+        <is>
+          <t>16:19</t>
+        </is>
+      </c>
+      <c r="T72" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq23映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±2分钟；反向位置物理seq38（站名待映射） ETA 7分钟参与校验</t>
+        </is>
+      </c>
       <c r="U72" s="2" t="inlineStr">
         <is>
           <t>15:22</t>
@@ -9106,7 +9134,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9145,7 +9173,7 @@
       </c>
       <c r="Z73" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA73" s="2" t="inlineStr">
@@ -9221,7 +9249,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9336,7 +9364,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9451,7 +9479,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9566,7 +9594,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9681,7 +9709,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9796,7 +9824,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9911,7 +9939,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -10026,7 +10054,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10141,7 +10169,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10195,7 +10223,7 @@
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -10256,7 +10284,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10310,7 +10338,927 @@
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>16/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr"/>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr"/>
+      <c r="K84" s="2" t="inlineStr"/>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr"/>
+      <c r="N84" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P84" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q84" s="2" t="inlineStr"/>
+      <c r="R84" s="2" t="inlineStr"/>
+      <c r="S84" s="2" t="inlineStr"/>
+      <c r="T84" s="2" t="inlineStr"/>
+      <c r="U84" s="2" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="V84" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W84" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y84" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z84" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA84" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB84" s="2" t="inlineStr">
+        <is>
+          <t>132.0</t>
+        </is>
+      </c>
+      <c r="AC84" s="2" t="inlineStr">
+        <is>
+          <t>16/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr"/>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>沪A68375D</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr"/>
+      <c r="K85" s="2" t="inlineStr"/>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr"/>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P85" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q85" s="2" t="inlineStr"/>
+      <c r="R85" s="2" t="inlineStr"/>
+      <c r="S85" s="2" t="inlineStr"/>
+      <c r="T85" s="2" t="inlineStr"/>
+      <c r="U85" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="V85" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W85" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y85" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z85" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA85" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB85" s="2" t="inlineStr">
+        <is>
+          <t>133.0</t>
+        </is>
+      </c>
+      <c r="AC85" s="2" t="inlineStr">
+        <is>
+          <t>20/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr"/>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>沪A09172D</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr"/>
+      <c r="K86" s="2" t="inlineStr"/>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr"/>
+      <c r="N86" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P86" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q86" s="2" t="inlineStr"/>
+      <c r="R86" s="2" t="inlineStr"/>
+      <c r="S86" s="2" t="inlineStr"/>
+      <c r="T86" s="2" t="inlineStr"/>
+      <c r="U86" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="V86" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W86" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y86" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z86" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA86" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB86" s="2" t="inlineStr">
+        <is>
+          <t>131.0</t>
+        </is>
+      </c>
+      <c r="AC86" s="2" t="inlineStr">
+        <is>
+          <t>14/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr"/>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>沪A02316D</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr"/>
+      <c r="K87" s="2" t="inlineStr"/>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr"/>
+      <c r="N87" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P87" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q87" s="2" t="inlineStr"/>
+      <c r="R87" s="2" t="inlineStr"/>
+      <c r="S87" s="2" t="inlineStr"/>
+      <c r="T87" s="2" t="inlineStr"/>
+      <c r="U87" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="V87" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W87" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y87" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z87" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA87" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB87" s="2" t="inlineStr">
+        <is>
+          <t>134.0</t>
+        </is>
+      </c>
+      <c r="AC87" s="2" t="inlineStr">
+        <is>
+          <t>24/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr"/>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>沪A02891D</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr"/>
+      <c r="K88" s="2" t="inlineStr"/>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr"/>
+      <c r="N88" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P88" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q88" s="2" t="inlineStr"/>
+      <c r="R88" s="2" t="inlineStr"/>
+      <c r="S88" s="2" t="inlineStr"/>
+      <c r="T88" s="2" t="inlineStr"/>
+      <c r="U88" s="2" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="V88" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W88" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y88" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z88" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA88" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB88" s="2" t="inlineStr">
+        <is>
+          <t>132.3</t>
+        </is>
+      </c>
+      <c r="AC88" s="2" t="inlineStr">
+        <is>
+          <t>19/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr"/>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>沪A05218D</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr"/>
+      <c r="K89" s="2" t="inlineStr"/>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr"/>
+      <c r="N89" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P89" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q89" s="2" t="inlineStr"/>
+      <c r="R89" s="2" t="inlineStr"/>
+      <c r="S89" s="2" t="inlineStr"/>
+      <c r="T89" s="2" t="inlineStr"/>
+      <c r="U89" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="V89" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W89" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y89" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z89" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA89" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB89" s="2" t="inlineStr">
+        <is>
+          <t>127.7</t>
+        </is>
+      </c>
+      <c r="AC89" s="2" t="inlineStr">
+        <is>
+          <t>6/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr"/>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>沪A90275D</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr"/>
+      <c r="K90" s="2" t="inlineStr"/>
+      <c r="L90" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr"/>
+      <c r="N90" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P90" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q90" s="2" t="inlineStr"/>
+      <c r="R90" s="2" t="inlineStr"/>
+      <c r="S90" s="2" t="inlineStr"/>
+      <c r="T90" s="2" t="inlineStr"/>
+      <c r="U90" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="V90" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W90" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y90" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z90" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA90" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB90" s="2" t="inlineStr">
+        <is>
+          <t>127.3</t>
+        </is>
+      </c>
+      <c r="AC90" s="2" t="inlineStr">
+        <is>
+          <t>5/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr"/>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr"/>
+      <c r="K91" s="2" t="inlineStr"/>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr"/>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P91" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q91" s="2" t="inlineStr"/>
+      <c r="R91" s="2" t="inlineStr"/>
+      <c r="S91" s="2" t="inlineStr"/>
+      <c r="T91" s="2" t="inlineStr"/>
+      <c r="U91" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="V91" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W91" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y91" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z91" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA91" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB91" s="2" t="inlineStr">
+        <is>
+          <t>140.0</t>
+        </is>
+      </c>
+      <c r="AC91" s="2" t="inlineStr">
+        <is>
+          <t>27/29</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-27-浦东35路.xlsx
+++ b/data/export/2026-09-27-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC91"/>
+  <dimension ref="A1:AC98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,17 +946,17 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>140.3</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1260,7 +1260,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1314,7 +1314,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1894,17 +1894,17 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>130.5</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
@@ -1970,7 +1970,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2030,17 +2030,17 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>27/29</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -2101,7 +2101,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2155,7 +2155,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -2220,7 +2220,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2274,7 +2274,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -2335,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2391,17 +2391,17 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>129.5</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -2462,7 +2462,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2581,7 +2581,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2620,14 +2620,14 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA18" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
           <t>128.7</t>
@@ -2635,7 +2635,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -2700,7 +2700,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2754,7 +2754,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -2819,7 +2819,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2863,17 +2863,17 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>136.5</t>
+          <t>142.7</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>25/29</t>
+          <t>27/29</t>
         </is>
       </c>
     </row>
@@ -3057,7 +3057,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3096,14 +3096,14 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA22" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
           <t>128.0</t>
@@ -3111,7 +3111,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -3176,7 +3176,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3215,14 +3215,14 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA23" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
           <t>126.7</t>
@@ -3230,7 +3230,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -3406,7 +3406,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3525,7 +3525,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3644,7 +3644,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3683,22 +3683,22 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA27" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -3817,7 +3817,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -4001,7 +4001,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4120,7 +4120,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4278,17 +4278,17 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA32" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>140.3</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
@@ -4477,7 +4477,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4650,7 +4650,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -4715,7 +4715,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4769,7 +4769,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -4949,7 +4949,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5004,7 +5004,7 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5115,17 +5115,17 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>130.5</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
@@ -5195,7 +5195,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5314,7 +5314,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5368,7 +5368,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -5433,7 +5433,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5487,7 +5487,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -5552,7 +5552,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5591,14 +5591,14 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA43" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
           <t>128.7</t>
@@ -5606,7 +5606,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -5671,7 +5671,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5790,7 +5790,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5834,17 +5834,17 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>136.5</t>
+          <t>142.7</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>25/29</t>
+          <t>27/29</t>
         </is>
       </c>
     </row>
@@ -5909,7 +5909,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5963,7 +5963,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -6147,7 +6147,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6186,14 +6186,14 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA48" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
           <t>128.0</t>
@@ -6201,7 +6201,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -6266,7 +6266,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6305,14 +6305,14 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA49" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
           <t>126.7</t>
@@ -6320,7 +6320,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -6385,7 +6385,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6558,7 +6558,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -6677,7 +6677,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -6861,7 +6861,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -7095,7 +7095,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7150,7 +7150,7 @@
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA56" s="2" t="inlineStr">
@@ -7226,7 +7226,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7345,7 +7345,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7389,17 +7389,17 @@
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>27/29</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -7464,7 +7464,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7518,7 +7518,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -7583,7 +7583,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7627,17 +7627,17 @@
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>129.5</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -7702,7 +7702,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7756,7 +7756,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -7821,7 +7821,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7860,14 +7860,14 @@
       </c>
       <c r="Z62" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA62" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
           <t>128.7</t>
@@ -7875,7 +7875,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -8059,7 +8059,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8098,14 +8098,14 @@
       </c>
       <c r="Z64" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA64" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA64" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
           <t>126.7</t>
@@ -8113,7 +8113,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -8232,7 +8232,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -8351,7 +8351,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -8416,7 +8416,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8654,7 +8654,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8892,7 +8892,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8946,7 +8946,7 @@
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -9007,7 +9007,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9062,7 +9062,7 @@
       </c>
       <c r="Z72" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA72" s="2" t="inlineStr">
@@ -9101,32 +9101,36 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>136分钟</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr"/>
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M73" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -9134,7 +9138,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9158,17 +9162,17 @@
       </c>
       <c r="W73" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y73" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z73" s="2" t="inlineStr">
@@ -9178,17 +9182,17 @@
       </c>
       <c r="AA73" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>27/29</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -9216,32 +9220,36 @@
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr"/>
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M74" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
           <t>06:40</t>
@@ -9249,7 +9257,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9273,32 +9281,32 @@
       </c>
       <c r="W74" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y74" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z74" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA74" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>130.5</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
@@ -9331,32 +9339,36 @@
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>135分钟</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr"/>
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M75" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -9364,7 +9376,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9388,37 +9400,37 @@
       </c>
       <c r="W75" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y75" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z75" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA75" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -9479,7 +9491,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9533,7 +9545,7 @@
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -9561,32 +9573,36 @@
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>134分钟</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr"/>
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M77" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -9594,7 +9610,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9618,17 +9634,17 @@
       </c>
       <c r="W77" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y77" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z77" s="2" t="inlineStr">
@@ -9638,17 +9654,17 @@
       </c>
       <c r="AA77" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>129.5</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -9676,32 +9692,36 @@
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:55</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>155分钟</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr"/>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M78" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -9709,7 +9729,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9733,17 +9753,17 @@
       </c>
       <c r="W78" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y78" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z78" s="2" t="inlineStr">
@@ -9753,17 +9773,17 @@
       </c>
       <c r="AA78" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>136.5</t>
+          <t>142.7</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>25/29</t>
+          <t>27/29</t>
         </is>
       </c>
     </row>
@@ -9791,32 +9811,36 @@
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>145分钟</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr"/>
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M79" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -9824,7 +9848,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9848,32 +9872,32 @@
       </c>
       <c r="W79" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y79" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z79" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA79" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA79" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>140.3</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
@@ -9939,7 +9963,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -10054,7 +10078,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10108,7 +10132,7 @@
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -10169,7 +10193,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10284,7 +10308,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10399,7 +10423,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10514,7 +10538,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10629,7 +10653,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10744,7 +10768,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10798,7 +10822,7 @@
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -10859,7 +10883,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10974,7 +10998,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11028,7 +11052,7 @@
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -11089,7 +11113,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11143,7 +11167,7 @@
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -11204,7 +11228,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11248,17 +11272,818 @@
       </c>
       <c r="AA91" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB91" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>27/29</t>
+          <t>25/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr"/>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>沪A79307D</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>18:12</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr"/>
+      <c r="K92" s="2" t="inlineStr"/>
+      <c r="L92" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr"/>
+      <c r="N92" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P92" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q92" s="2" t="inlineStr"/>
+      <c r="R92" s="2" t="inlineStr"/>
+      <c r="S92" s="2" t="inlineStr"/>
+      <c r="T92" s="2" t="inlineStr"/>
+      <c r="U92" s="2" t="inlineStr">
+        <is>
+          <t>18:12</t>
+        </is>
+      </c>
+      <c r="V92" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W92" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y92" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z92" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA92" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB92" s="2" t="inlineStr"/>
+      <c r="AC92" s="2" t="inlineStr">
+        <is>
+          <t>—/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr"/>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>沪A67057D</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr"/>
+      <c r="K93" s="2" t="inlineStr"/>
+      <c r="L93" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr"/>
+      <c r="N93" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P93" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q93" s="2" t="inlineStr"/>
+      <c r="R93" s="2" t="inlineStr"/>
+      <c r="S93" s="2" t="inlineStr"/>
+      <c r="T93" s="2" t="inlineStr"/>
+      <c r="U93" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="V93" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W93" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y93" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z93" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA93" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB93" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
+      <c r="AC93" s="2" t="inlineStr">
+        <is>
+          <t>6/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr"/>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>沪A51682D</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr"/>
+      <c r="K94" s="2" t="inlineStr"/>
+      <c r="L94" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr"/>
+      <c r="N94" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P94" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q94" s="2" t="inlineStr"/>
+      <c r="R94" s="2" t="inlineStr"/>
+      <c r="S94" s="2" t="inlineStr"/>
+      <c r="T94" s="2" t="inlineStr"/>
+      <c r="U94" s="2" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="V94" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W94" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y94" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z94" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA94" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB94" s="2" t="inlineStr">
+        <is>
+          <t>126.7</t>
+        </is>
+      </c>
+      <c r="AC94" s="2" t="inlineStr">
+        <is>
+          <t>3/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr"/>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>沪A95621D</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr"/>
+      <c r="K95" s="2" t="inlineStr"/>
+      <c r="L95" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr"/>
+      <c r="N95" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P95" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q95" s="2" t="inlineStr"/>
+      <c r="R95" s="2" t="inlineStr"/>
+      <c r="S95" s="2" t="inlineStr"/>
+      <c r="T95" s="2" t="inlineStr"/>
+      <c r="U95" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="V95" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W95" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y95" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z95" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA95" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB95" s="2" t="inlineStr">
+        <is>
+          <t>128.7</t>
+        </is>
+      </c>
+      <c r="AC95" s="2" t="inlineStr">
+        <is>
+          <t>9/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr"/>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>沪A67672D</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>18:50</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr"/>
+      <c r="K96" s="2" t="inlineStr"/>
+      <c r="L96" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr"/>
+      <c r="N96" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P96" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q96" s="2" t="inlineStr"/>
+      <c r="R96" s="2" t="inlineStr"/>
+      <c r="S96" s="2" t="inlineStr"/>
+      <c r="T96" s="2" t="inlineStr"/>
+      <c r="U96" s="2" t="inlineStr">
+        <is>
+          <t>18:50</t>
+        </is>
+      </c>
+      <c r="V96" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W96" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y96" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z96" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA96" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB96" s="2" t="inlineStr">
+        <is>
+          <t>134.0</t>
+        </is>
+      </c>
+      <c r="AC96" s="2" t="inlineStr">
+        <is>
+          <t>23/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr"/>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>沪A71572D</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr"/>
+      <c r="K97" s="2" t="inlineStr"/>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr"/>
+      <c r="N97" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="O97" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P97" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q97" s="2" t="inlineStr"/>
+      <c r="R97" s="2" t="inlineStr"/>
+      <c r="S97" s="2" t="inlineStr"/>
+      <c r="T97" s="2" t="inlineStr"/>
+      <c r="U97" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="V97" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W97" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y97" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z97" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA97" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB97" s="2" t="inlineStr">
+        <is>
+          <t>130.5</t>
+        </is>
+      </c>
+      <c r="AC97" s="2" t="inlineStr">
+        <is>
+          <t>11/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr"/>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>沪A62981D</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr"/>
+      <c r="K98" s="2" t="inlineStr"/>
+      <c r="L98" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr"/>
+      <c r="N98" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O98" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P98" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q98" s="2" t="inlineStr"/>
+      <c r="R98" s="2" t="inlineStr"/>
+      <c r="S98" s="2" t="inlineStr"/>
+      <c r="T98" s="2" t="inlineStr"/>
+      <c r="U98" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="V98" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W98" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y98" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z98" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA98" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB98" s="2" t="inlineStr">
+        <is>
+          <t>140.3</t>
+        </is>
+      </c>
+      <c r="AC98" s="2" t="inlineStr">
+        <is>
+          <t>26/29</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-27-浦东35路.xlsx
+++ b/data/export/2026-09-27-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC98"/>
+  <dimension ref="A1:AC105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -956,12 +956,12 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>140.3</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>26/29</t>
+          <t>27/29</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1260,7 +1260,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1299,22 +1299,22 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1775,17 +1775,17 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>131.7</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1970,7 +1970,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2101,7 +2101,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2220,7 +2220,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2259,7 +2259,7 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
@@ -2335,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
@@ -2401,7 +2401,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -2462,7 +2462,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2581,7 +2581,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2635,7 +2635,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -2700,7 +2700,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2819,7 +2819,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2858,22 +2858,22 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA20" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>142.7</t>
+          <t>139.3</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>27/29</t>
+          <t>26/29</t>
         </is>
       </c>
     </row>
@@ -3057,7 +3057,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3176,7 +3176,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3406,7 +3406,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3445,7 +3445,7 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
@@ -3525,7 +3525,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3569,12 +3569,12 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>131.7</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
@@ -3644,7 +3644,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3936,7 +3936,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -4001,7 +4001,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4055,7 +4055,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -4120,7 +4120,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4159,22 +4159,22 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA31" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>132.3</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -4239,7 +4239,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4288,12 +4288,12 @@
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>140.3</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>26/29</t>
+          <t>27/29</t>
         </is>
       </c>
     </row>
@@ -4477,7 +4477,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4715,7 +4715,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4754,22 +4754,22 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -4949,7 +4949,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5195,7 +5195,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5234,17 +5234,17 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA40" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>131.7</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
@@ -5314,7 +5314,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5353,7 +5353,7 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
@@ -5433,7 +5433,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5552,7 +5552,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -5671,7 +5671,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5790,7 +5790,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5829,22 +5829,22 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA45" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>142.7</t>
+          <t>139.3</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>27/29</t>
+          <t>26/29</t>
         </is>
       </c>
     </row>
@@ -5909,7 +5909,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -6147,7 +6147,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6266,7 +6266,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6385,7 +6385,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6424,7 +6424,7 @@
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA50" s="2" t="inlineStr">
@@ -6677,7 +6677,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -6861,7 +6861,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6900,22 +6900,22 @@
       </c>
       <c r="Z54" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA54" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>132.3</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -7095,7 +7095,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7226,7 +7226,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7345,7 +7345,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7464,7 +7464,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7583,7 +7583,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7622,7 +7622,7 @@
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA60" s="2" t="inlineStr">
@@ -7637,7 +7637,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -7702,7 +7702,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7821,7 +7821,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7875,7 +7875,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -8059,7 +8059,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8232,7 +8232,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -8416,7 +8416,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8460,12 +8460,12 @@
       </c>
       <c r="AA67" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>131.7</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
@@ -8654,7 +8654,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8708,7 +8708,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -8892,7 +8892,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -9007,7 +9007,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9138,7 +9138,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9257,7 +9257,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9376,7 +9376,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9491,7 +9491,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9530,7 +9530,7 @@
       </c>
       <c r="Z76" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA76" s="2" t="inlineStr">
@@ -9610,7 +9610,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9649,7 +9649,7 @@
       </c>
       <c r="Z77" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA77" s="2" t="inlineStr">
@@ -9664,7 +9664,7 @@
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -9702,24 +9702,24 @@
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>18:55</t>
+          <t>18:45</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>155分钟</t>
+          <t>145分钟</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr"/>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -9729,7 +9729,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9768,22 +9768,22 @@
       </c>
       <c r="Z78" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA78" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA78" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>142.7</t>
+          <t>139.3</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>27/29</t>
+          <t>26/29</t>
         </is>
       </c>
     </row>
@@ -9821,24 +9821,24 @@
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>18:52</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>145分钟</t>
+          <t>147分钟</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr"/>
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
@@ -9848,7 +9848,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9897,12 +9897,12 @@
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>140.3</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>26/29</t>
+          <t>27/29</t>
         </is>
       </c>
     </row>
@@ -9963,7 +9963,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -10002,7 +10002,7 @@
       </c>
       <c r="Z80" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA80" s="2" t="inlineStr">
@@ -10045,32 +10045,36 @@
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:57</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr"/>
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M81" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -10078,7 +10082,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10102,37 +10106,37 @@
       </c>
       <c r="W81" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y81" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z81" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA81" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -10160,32 +10164,36 @@
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr"/>
       <c r="K82" s="2" t="inlineStr"/>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M82" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
           <t>06:40</t>
@@ -10193,7 +10201,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10217,32 +10225,32 @@
       </c>
       <c r="W82" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y82" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z82" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA82" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA82" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>131.7</t>
         </is>
       </c>
       <c r="AC82" s="2" t="inlineStr">
@@ -10275,32 +10283,36 @@
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:13</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr"/>
       <c r="K83" s="2" t="inlineStr"/>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M83" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
           <t>06:40</t>
@@ -10308,7 +10320,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10332,37 +10344,37 @@
       </c>
       <c r="W83" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y83" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z83" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA83" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA83" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB83" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>132.3</t>
         </is>
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -10390,32 +10402,36 @@
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:26</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr"/>
       <c r="K84" s="2" t="inlineStr"/>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M84" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N84" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -10423,7 +10439,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10447,17 +10463,17 @@
       </c>
       <c r="W84" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y84" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z84" s="2" t="inlineStr">
@@ -10467,12 +10483,12 @@
       </c>
       <c r="AA84" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB84" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>131.7</t>
         </is>
       </c>
       <c r="AC84" s="2" t="inlineStr">
@@ -10538,7 +10554,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10653,7 +10669,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10768,7 +10784,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10883,7 +10899,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10937,7 +10953,7 @@
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -10998,7 +11014,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11113,7 +11129,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11228,7 +11244,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11343,7 +11359,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11454,7 +11470,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11569,7 +11585,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11684,7 +11700,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11738,7 +11754,7 @@
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -11799,7 +11815,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11914,7 +11930,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -11976,22 +11992,22 @@
       <c r="A98" s="2" t="inlineStr"/>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>沪A62981D</t>
+          <t>沪A15790A</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>19:10</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="D98" s="2" t="inlineStr">
-        <is>
-          <t>19:15</t>
-        </is>
-      </c>
-      <c r="E98" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
@@ -12024,12 +12040,12 @@
       <c r="M98" s="2" t="inlineStr"/>
       <c r="N98" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12043,47 +12059,852 @@
       <c r="T98" s="2" t="inlineStr"/>
       <c r="U98" s="2" t="inlineStr">
         <is>
+          <t>19:10</t>
+        </is>
+      </c>
+      <c r="V98" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W98" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y98" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z98" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA98" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB98" s="2" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
+      <c r="AC98" s="2" t="inlineStr">
+        <is>
+          <t>2/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr"/>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>沪A62981D</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
           <t>19:15</t>
         </is>
       </c>
-      <c r="V98" s="2" t="inlineStr">
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr"/>
+      <c r="K99" s="2" t="inlineStr"/>
+      <c r="L99" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr"/>
+      <c r="N99" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O99" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="P99" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q99" s="2" t="inlineStr"/>
+      <c r="R99" s="2" t="inlineStr"/>
+      <c r="S99" s="2" t="inlineStr"/>
+      <c r="T99" s="2" t="inlineStr"/>
+      <c r="U99" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="V99" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W98" s="2" t="inlineStr">
+      <c r="W99" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X98" s="2" t="inlineStr">
+      <c r="X99" s="2" t="inlineStr">
         <is>
           <t>待确认</t>
         </is>
       </c>
-      <c r="Y98" s="2" t="inlineStr">
+      <c r="Y99" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z98" s="2" t="inlineStr">
+      <c r="Z99" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA98" s="2" t="inlineStr">
+      <c r="AA99" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AB98" s="2" t="inlineStr">
-        <is>
-          <t>140.3</t>
-        </is>
-      </c>
-      <c r="AC98" s="2" t="inlineStr">
+      <c r="AB99" s="2" t="inlineStr">
+        <is>
+          <t>141.0</t>
+        </is>
+      </c>
+      <c r="AC99" s="2" t="inlineStr">
+        <is>
+          <t>27/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr"/>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>沪A70597D</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="inlineStr"/>
+      <c r="K100" s="2" t="inlineStr"/>
+      <c r="L100" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="inlineStr"/>
+      <c r="N100" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O100" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="P100" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q100" s="2" t="inlineStr"/>
+      <c r="R100" s="2" t="inlineStr"/>
+      <c r="S100" s="2" t="inlineStr"/>
+      <c r="T100" s="2" t="inlineStr"/>
+      <c r="U100" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="V100" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W100" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y100" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z100" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA100" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB100" s="2" t="inlineStr">
+        <is>
+          <t>130.5</t>
+        </is>
+      </c>
+      <c r="AC100" s="2" t="inlineStr">
+        <is>
+          <t>11/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr"/>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>沪A37267D</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="inlineStr"/>
+      <c r="K101" s="2" t="inlineStr"/>
+      <c r="L101" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="inlineStr"/>
+      <c r="N101" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O101" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="P101" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q101" s="2" t="inlineStr"/>
+      <c r="R101" s="2" t="inlineStr"/>
+      <c r="S101" s="2" t="inlineStr"/>
+      <c r="T101" s="2" t="inlineStr"/>
+      <c r="U101" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="V101" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W101" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y101" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z101" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA101" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB101" s="2" t="inlineStr">
+        <is>
+          <t>129.5</t>
+        </is>
+      </c>
+      <c r="AC101" s="2" t="inlineStr">
+        <is>
+          <t>9/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr"/>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>沪A67712D</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="inlineStr"/>
+      <c r="K102" s="2" t="inlineStr"/>
+      <c r="L102" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M102" s="2" t="inlineStr"/>
+      <c r="N102" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="O102" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="P102" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q102" s="2" t="inlineStr"/>
+      <c r="R102" s="2" t="inlineStr"/>
+      <c r="S102" s="2" t="inlineStr"/>
+      <c r="T102" s="2" t="inlineStr"/>
+      <c r="U102" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="V102" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W102" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y102" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z102" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA102" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB102" s="2" t="inlineStr">
+        <is>
+          <t>132.3</t>
+        </is>
+      </c>
+      <c r="AC102" s="2" t="inlineStr">
+        <is>
+          <t>18/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr"/>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>沪A62217D</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="inlineStr"/>
+      <c r="K103" s="2" t="inlineStr"/>
+      <c r="L103" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M103" s="2" t="inlineStr"/>
+      <c r="N103" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O103" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="P103" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q103" s="2" t="inlineStr"/>
+      <c r="R103" s="2" t="inlineStr"/>
+      <c r="S103" s="2" t="inlineStr"/>
+      <c r="T103" s="2" t="inlineStr"/>
+      <c r="U103" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="V103" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W103" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y103" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z103" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA103" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB103" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
+      <c r="AC103" s="2" t="inlineStr">
+        <is>
+          <t>10/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr"/>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>沪A73927D</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J104" s="2" t="inlineStr"/>
+      <c r="K104" s="2" t="inlineStr"/>
+      <c r="L104" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M104" s="2" t="inlineStr"/>
+      <c r="N104" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O104" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="P104" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q104" s="2" t="inlineStr"/>
+      <c r="R104" s="2" t="inlineStr"/>
+      <c r="S104" s="2" t="inlineStr"/>
+      <c r="T104" s="2" t="inlineStr"/>
+      <c r="U104" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="V104" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W104" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y104" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z104" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA104" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB104" s="2" t="inlineStr">
+        <is>
+          <t>139.3</t>
+        </is>
+      </c>
+      <c r="AC104" s="2" t="inlineStr">
         <is>
           <t>26/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr"/>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>沪A11062A</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>20:05</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J105" s="2" t="inlineStr"/>
+      <c r="K105" s="2" t="inlineStr"/>
+      <c r="L105" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M105" s="2" t="inlineStr"/>
+      <c r="N105" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="O105" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="P105" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q105" s="2" t="inlineStr"/>
+      <c r="R105" s="2" t="inlineStr"/>
+      <c r="S105" s="2" t="inlineStr"/>
+      <c r="T105" s="2" t="inlineStr"/>
+      <c r="U105" s="2" t="inlineStr">
+        <is>
+          <t>20:05</t>
+        </is>
+      </c>
+      <c r="V105" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W105" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y105" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z105" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA105" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB105" s="2" t="inlineStr">
+        <is>
+          <t>131.7</t>
+        </is>
+      </c>
+      <c r="AC105" s="2" t="inlineStr">
+        <is>
+          <t>16/29</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-27-浦东35路.xlsx
+++ b/data/export/2026-09-27-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC105"/>
+  <dimension ref="A1:AC108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -832,17 +832,17 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>132.3</t>
+          <t>133.5</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1189,12 +1189,12 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>132.8</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
@@ -1260,7 +1260,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1379,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>127.3</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -1552,7 +1552,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1790,7 +1790,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -1855,7 +1855,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -2101,7 +2101,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2145,17 +2145,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>133.3</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -2220,7 +2220,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2335,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2462,7 +2462,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
@@ -2581,7 +2581,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2635,7 +2635,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -2700,7 +2700,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2819,7 +2819,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2938,7 +2938,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2977,7 +2977,7 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
@@ -3057,7 +3057,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3096,22 +3096,22 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA22" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>128.7</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -3176,7 +3176,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3220,17 +3220,17 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>126.7</t>
+          <t>127.2</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -3406,7 +3406,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3579,7 +3579,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -3644,7 +3644,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3688,17 +3688,17 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -3817,7 +3817,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -4001,7 +4001,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>132.3</t>
+          <t>133.5</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -4120,7 +4120,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4174,7 +4174,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -4239,7 +4239,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4477,7 +4477,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4521,12 +4521,12 @@
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>132.8</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4640,17 +4640,17 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>127.3</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -4715,7 +4715,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4888,7 +4888,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -4949,7 +4949,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5195,7 +5195,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5249,7 +5249,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -5314,7 +5314,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5433,7 +5433,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5477,17 +5477,17 @@
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>133.3</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -5552,7 +5552,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -5671,7 +5671,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5710,7 +5710,7 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA44" s="2" t="inlineStr">
@@ -5790,7 +5790,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5909,7 +5909,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -6028,7 +6028,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6067,7 +6067,7 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA47" s="2" t="inlineStr">
@@ -6147,7 +6147,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6186,22 +6186,22 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA48" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>128.7</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -6266,7 +6266,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6310,17 +6310,17 @@
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>126.7</t>
+          <t>127.2</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -6385,7 +6385,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6558,7 +6558,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -6677,7 +6677,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -6861,7 +6861,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6915,7 +6915,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -7034,7 +7034,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -7095,7 +7095,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7226,7 +7226,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7270,12 +7270,12 @@
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>132.8</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
@@ -7464,7 +7464,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7508,17 +7508,17 @@
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>133.3</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -7583,7 +7583,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7702,7 +7702,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7821,7 +7821,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7875,7 +7875,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -7940,7 +7940,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7979,7 +7979,7 @@
       </c>
       <c r="Z63" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA63" s="2" t="inlineStr">
@@ -8059,7 +8059,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8103,17 +8103,17 @@
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>126.7</t>
+          <t>127.2</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -8232,7 +8232,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -8351,7 +8351,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -8470,7 +8470,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -8654,7 +8654,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8698,17 +8698,17 @@
       </c>
       <c r="AA69" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>132.3</t>
+          <t>133.5</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -8827,7 +8827,7 @@
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -8892,7 +8892,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8936,17 +8936,17 @@
       </c>
       <c r="AA71" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>127.3</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -9007,7 +9007,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9257,7 +9257,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9376,7 +9376,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9420,17 +9420,17 @@
       </c>
       <c r="AA75" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9610,7 +9610,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9729,7 +9729,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9848,7 +9848,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9963,7 +9963,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -10082,7 +10082,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10201,7 +10201,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10255,7 +10255,7 @@
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -10320,7 +10320,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10374,7 +10374,7 @@
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -10493,7 +10493,7 @@
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -10521,32 +10521,36 @@
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr"/>
       <c r="K85" s="2" t="inlineStr"/>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M85" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -10554,7 +10558,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10578,17 +10582,17 @@
       </c>
       <c r="W85" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y85" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z85" s="2" t="inlineStr">
@@ -10598,12 +10602,12 @@
       </c>
       <c r="AA85" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB85" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>132.8</t>
         </is>
       </c>
       <c r="AC85" s="2" t="inlineStr">
@@ -10669,7 +10673,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10708,7 +10712,7 @@
       </c>
       <c r="Z86" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA86" s="2" t="inlineStr">
@@ -10751,32 +10755,36 @@
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:52</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr"/>
       <c r="K87" s="2" t="inlineStr"/>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M87" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -10784,7 +10792,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10808,17 +10816,17 @@
       </c>
       <c r="W87" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y87" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z87" s="2" t="inlineStr">
@@ -10828,17 +10836,17 @@
       </c>
       <c r="AA87" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB87" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>133.3</t>
         </is>
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -10866,32 +10874,36 @@
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>137分钟</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr"/>
       <c r="K88" s="2" t="inlineStr"/>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M88" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N88" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -10899,7 +10911,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10923,17 +10935,17 @@
       </c>
       <c r="W88" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y88" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z88" s="2" t="inlineStr">
@@ -10943,17 +10955,17 @@
       </c>
       <c r="AA88" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB88" s="2" t="inlineStr">
         <is>
-          <t>132.3</t>
+          <t>133.5</t>
         </is>
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -11014,7 +11026,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11096,32 +11108,36 @@
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:06</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr"/>
       <c r="K90" s="2" t="inlineStr"/>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M90" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N90" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -11129,7 +11145,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11153,17 +11169,17 @@
       </c>
       <c r="W90" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y90" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z90" s="2" t="inlineStr">
@@ -11173,17 +11189,17 @@
       </c>
       <c r="AA90" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB90" s="2" t="inlineStr">
         <is>
-          <t>127.3</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -11326,12 +11342,12 @@
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq38推进至seq58，推进20站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
@@ -11359,7 +11375,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11367,10 +11383,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q92" s="2" t="inlineStr"/>
-      <c r="R92" s="2" t="inlineStr"/>
-      <c r="S92" s="2" t="inlineStr"/>
-      <c r="T92" s="2" t="inlineStr"/>
+      <c r="Q92" s="2" t="inlineStr">
+        <is>
+          <t>物理seq24（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R92" s="2" t="inlineStr">
+        <is>
+          <t>19:04</t>
+        </is>
+      </c>
+      <c r="S92" s="2" t="inlineStr">
+        <is>
+          <t>19:12</t>
+        </is>
+      </c>
+      <c r="T92" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq24映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±8分钟；反向位置物理seq38（站名待映射） ETA 7分钟参与校验</t>
+        </is>
+      </c>
       <c r="U92" s="2" t="inlineStr">
         <is>
           <t>18:12</t>
@@ -11437,32 +11469,36 @@
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr"/>
       <c r="K93" s="2" t="inlineStr"/>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M93" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N93" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -11470,7 +11506,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11494,37 +11530,37 @@
       </c>
       <c r="W93" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y93" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z93" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA93" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA93" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB93" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>128.7</t>
         </is>
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -11552,32 +11588,36 @@
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:34</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr"/>
       <c r="K94" s="2" t="inlineStr"/>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M94" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N94" s="2" t="inlineStr">
         <is>
           <t>06:40</t>
@@ -11585,7 +11625,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11609,17 +11649,17 @@
       </c>
       <c r="W94" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y94" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z94" s="2" t="inlineStr">
@@ -11629,17 +11669,17 @@
       </c>
       <c r="AA94" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB94" s="2" t="inlineStr">
         <is>
-          <t>126.7</t>
+          <t>127.2</t>
         </is>
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -11700,7 +11740,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11754,7 +11794,7 @@
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -11782,32 +11822,36 @@
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:55</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr"/>
       <c r="K96" s="2" t="inlineStr"/>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M96" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N96" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -11815,7 +11859,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11839,17 +11883,17 @@
       </c>
       <c r="W96" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y96" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z96" s="2" t="inlineStr">
@@ -11859,17 +11903,17 @@
       </c>
       <c r="AA96" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB96" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -11930,7 +11974,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -12012,12 +12056,12 @@
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程49%处后消失；随后反向物理轨迹由seq28推进至seq30，推进2站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
@@ -12045,7 +12089,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12053,10 +12097,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q98" s="2" t="inlineStr"/>
-      <c r="R98" s="2" t="inlineStr"/>
-      <c r="S98" s="2" t="inlineStr"/>
-      <c r="T98" s="2" t="inlineStr"/>
+      <c r="Q98" s="2" t="inlineStr">
+        <is>
+          <t>物理seq32（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R98" s="2" t="inlineStr">
+        <is>
+          <t>20:02</t>
+        </is>
+      </c>
+      <c r="S98" s="2" t="inlineStr">
+        <is>
+          <t>20:06</t>
+        </is>
+      </c>
+      <c r="T98" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq32映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±4分钟；反向位置物理seq28（站名待映射） ETA 0分钟参与校验</t>
+        </is>
+      </c>
       <c r="U98" s="2" t="inlineStr">
         <is>
           <t>19:10</t>
@@ -12160,7 +12220,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12275,7 +12335,7 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
@@ -12390,7 +12450,7 @@
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
@@ -12505,7 +12565,7 @@
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
@@ -12559,7 +12619,7 @@
       </c>
       <c r="AC102" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -12620,7 +12680,7 @@
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P103" s="2" t="inlineStr">
@@ -12735,7 +12795,7 @@
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P104" s="2" t="inlineStr">
@@ -12797,22 +12857,22 @@
       <c r="A105" s="2" t="inlineStr"/>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>沪A11062A</t>
+          <t>沪A36993D</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="D105" s="2" t="inlineStr">
-        <is>
-          <t>20:05</t>
-        </is>
-      </c>
-      <c r="E105" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="F105" s="2" t="inlineStr">
@@ -12845,12 +12905,12 @@
       <c r="M105" s="2" t="inlineStr"/>
       <c r="N105" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P105" s="2" t="inlineStr">
@@ -12864,47 +12924,392 @@
       <c r="T105" s="2" t="inlineStr"/>
       <c r="U105" s="2" t="inlineStr">
         <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="V105" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W105" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y105" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z105" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA105" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB105" s="2" t="inlineStr">
+        <is>
+          <t>130.7</t>
+        </is>
+      </c>
+      <c r="AC105" s="2" t="inlineStr">
+        <is>
+          <t>13/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr"/>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>沪A11062A</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
           <t>20:05</t>
         </is>
       </c>
-      <c r="V105" s="2" t="inlineStr">
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J106" s="2" t="inlineStr"/>
+      <c r="K106" s="2" t="inlineStr"/>
+      <c r="L106" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M106" s="2" t="inlineStr"/>
+      <c r="N106" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="O106" s="2" t="inlineStr">
+        <is>
+          <t>20:21</t>
+        </is>
+      </c>
+      <c r="P106" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q106" s="2" t="inlineStr"/>
+      <c r="R106" s="2" t="inlineStr"/>
+      <c r="S106" s="2" t="inlineStr"/>
+      <c r="T106" s="2" t="inlineStr"/>
+      <c r="U106" s="2" t="inlineStr">
+        <is>
+          <t>20:05</t>
+        </is>
+      </c>
+      <c r="V106" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W105" s="2" t="inlineStr">
+      <c r="W106" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X105" s="2" t="inlineStr">
+      <c r="X106" s="2" t="inlineStr">
         <is>
           <t>待确认</t>
         </is>
       </c>
-      <c r="Y105" s="2" t="inlineStr">
+      <c r="Y106" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z105" s="2" t="inlineStr">
+      <c r="Z106" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA105" s="2" t="inlineStr">
+      <c r="AA106" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AB105" s="2" t="inlineStr">
+      <c r="AB106" s="2" t="inlineStr">
         <is>
           <t>131.7</t>
         </is>
       </c>
-      <c r="AC105" s="2" t="inlineStr">
-        <is>
-          <t>16/29</t>
+      <c r="AC106" s="2" t="inlineStr">
+        <is>
+          <t>17/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr"/>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>沪A09172D</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H107" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I107" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J107" s="2" t="inlineStr"/>
+      <c r="K107" s="2" t="inlineStr"/>
+      <c r="L107" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M107" s="2" t="inlineStr"/>
+      <c r="N107" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O107" s="2" t="inlineStr">
+        <is>
+          <t>20:21</t>
+        </is>
+      </c>
+      <c r="P107" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q107" s="2" t="inlineStr"/>
+      <c r="R107" s="2" t="inlineStr"/>
+      <c r="S107" s="2" t="inlineStr"/>
+      <c r="T107" s="2" t="inlineStr"/>
+      <c r="U107" s="2" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="V107" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W107" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X107" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y107" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z107" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA107" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB107" s="2" t="inlineStr">
+        <is>
+          <t>131.0</t>
+        </is>
+      </c>
+      <c r="AC107" s="2" t="inlineStr">
+        <is>
+          <t>14/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr"/>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>沪A67057D</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>20:55</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H108" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I108" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J108" s="2" t="inlineStr"/>
+      <c r="K108" s="2" t="inlineStr"/>
+      <c r="L108" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M108" s="2" t="inlineStr"/>
+      <c r="N108" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O108" s="2" t="inlineStr">
+        <is>
+          <t>20:21</t>
+        </is>
+      </c>
+      <c r="P108" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q108" s="2" t="inlineStr"/>
+      <c r="R108" s="2" t="inlineStr"/>
+      <c r="S108" s="2" t="inlineStr"/>
+      <c r="T108" s="2" t="inlineStr"/>
+      <c r="U108" s="2" t="inlineStr">
+        <is>
+          <t>20:55</t>
+        </is>
+      </c>
+      <c r="V108" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W108" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X108" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y108" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z108" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA108" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB108" s="2" t="inlineStr">
+        <is>
+          <t>128.7</t>
+        </is>
+      </c>
+      <c r="AC108" s="2" t="inlineStr">
+        <is>
+          <t>7/29</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-27-浦东35路.xlsx
+++ b/data/export/2026-09-27-浦东35路.xlsx
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1260,7 +1260,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1314,7 +1314,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -1433,7 +1433,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -1552,7 +1552,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1790,7 +1790,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -1855,7 +1855,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1899,17 +1899,17 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>130.5</t>
+          <t>128.3</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -2220,7 +2220,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2274,7 +2274,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -2335,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2462,7 +2462,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2581,7 +2581,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2625,17 +2625,17 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>128.7</t>
+          <t>127.8</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -2819,7 +2819,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2938,7 +2938,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -3057,7 +3057,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3106,12 +3106,12 @@
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>128.7</t>
+          <t>129.7</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -3176,7 +3176,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3225,12 +3225,12 @@
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>127.2</t>
+          <t>126.8</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -3406,7 +3406,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3579,7 +3579,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -3644,7 +3644,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3693,12 +3693,12 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>131.7</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -4120,7 +4120,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4650,7 +4650,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -4715,7 +4715,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4769,7 +4769,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -4888,7 +4888,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -5076,7 +5076,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5120,17 +5120,17 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>130.5</t>
+          <t>128.3</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -5195,7 +5195,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5249,7 +5249,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -5314,7 +5314,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5368,7 +5368,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -5552,7 +5552,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5596,17 +5596,17 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>128.7</t>
+          <t>127.8</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -5671,7 +5671,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5790,7 +5790,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -6028,7 +6028,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6147,7 +6147,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6196,12 +6196,12 @@
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>128.7</t>
+          <t>129.7</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -6266,7 +6266,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6315,12 +6315,12 @@
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>127.2</t>
+          <t>126.8</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -6385,7 +6385,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6677,7 +6677,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -6861,7 +6861,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -7034,7 +7034,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -7583,7 +7583,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7821,7 +7821,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7865,17 +7865,17 @@
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>128.7</t>
+          <t>127.8</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -7940,7 +7940,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -8059,7 +8059,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8108,12 +8108,12 @@
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>127.2</t>
+          <t>126.8</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -8232,7 +8232,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -8470,7 +8470,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -8827,7 +8827,7 @@
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -8946,7 +8946,7 @@
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -9257,7 +9257,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9301,17 +9301,17 @@
       </c>
       <c r="AA74" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>130.5</t>
+          <t>128.3</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -9376,7 +9376,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9425,12 +9425,12 @@
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>131.7</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9545,7 +9545,7 @@
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -9610,7 +9610,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9729,7 +9729,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9848,7 +9848,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9963,7 +9963,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -10082,7 +10082,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10136,7 +10136,7 @@
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -10201,7 +10201,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10255,7 +10255,7 @@
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -10320,7 +10320,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10493,7 +10493,7 @@
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -10673,7 +10673,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -11199,7 +11199,7 @@
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -11479,24 +11479,24 @@
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:33</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>130分钟</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr"/>
       <c r="K93" s="2" t="inlineStr"/>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N93" s="2" t="inlineStr">
@@ -11506,7 +11506,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11555,12 +11555,12 @@
       </c>
       <c r="AB93" s="2" t="inlineStr">
         <is>
-          <t>128.7</t>
+          <t>129.7</t>
         </is>
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -11598,24 +11598,24 @@
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>20:34</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>129分钟</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr"/>
       <c r="K94" s="2" t="inlineStr"/>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N94" s="2" t="inlineStr">
@@ -11625,7 +11625,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11674,12 +11674,12 @@
       </c>
       <c r="AB94" s="2" t="inlineStr">
         <is>
-          <t>127.2</t>
+          <t>126.8</t>
         </is>
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -11707,32 +11707,36 @@
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:45</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr"/>
       <c r="K95" s="2" t="inlineStr"/>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M95" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N95" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -11740,7 +11744,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11764,17 +11768,17 @@
       </c>
       <c r="W95" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y95" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z95" s="2" t="inlineStr">
@@ -11784,17 +11788,17 @@
       </c>
       <c r="AA95" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB95" s="2" t="inlineStr">
         <is>
-          <t>128.7</t>
+          <t>127.8</t>
         </is>
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -11832,12 +11836,12 @@
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>20:55</t>
+          <t>20:57</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>125分钟</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr"/>
@@ -11859,7 +11863,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11908,12 +11912,12 @@
       </c>
       <c r="AB96" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>131.7</t>
         </is>
       </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -11941,32 +11945,36 @@
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:04</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr"/>
       <c r="K97" s="2" t="inlineStr"/>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M97" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N97" s="2" t="inlineStr">
         <is>
           <t>06:40</t>
@@ -11974,7 +11982,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -11998,17 +12006,17 @@
       </c>
       <c r="W97" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y97" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z97" s="2" t="inlineStr">
@@ -12018,17 +12026,17 @@
       </c>
       <c r="AA97" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB97" s="2" t="inlineStr">
         <is>
-          <t>130.5</t>
+          <t>128.3</t>
         </is>
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -12061,7 +12069,7 @@
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程49%处后消失；随后反向物理轨迹由seq28推进至seq30，推进2站，达到≥2站确认条件</t>
+          <t>原方向在全程49%处后消失；随后反向物理轨迹由seq28推进至seq50，推进22站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
@@ -12089,7 +12097,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12220,7 +12228,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12335,7 +12343,7 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
@@ -12389,7 +12397,7 @@
       </c>
       <c r="AC100" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -12450,7 +12458,7 @@
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
@@ -12532,12 +12540,12 @@
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程51%处后消失；随后反向物理轨迹由seq28推进至seq37，推进9站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
@@ -12565,18 +12573,34 @@
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
+          <t>20:51</t>
+        </is>
+      </c>
+      <c r="P102" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q102" s="2" t="inlineStr">
+        <is>
+          <t>迎春路长柳路</t>
+        </is>
+      </c>
+      <c r="R102" s="2" t="inlineStr">
+        <is>
           <t>20:21</t>
         </is>
       </c>
-      <c r="P102" s="2" t="inlineStr">
-        <is>
-          <t>SHMAAS</t>
-        </is>
-      </c>
-      <c r="Q102" s="2" t="inlineStr"/>
-      <c r="R102" s="2" t="inlineStr"/>
-      <c r="S102" s="2" t="inlineStr"/>
-      <c r="T102" s="2" t="inlineStr"/>
+      <c r="S102" s="2" t="inlineStr">
+        <is>
+          <t>20:26</t>
+        </is>
+      </c>
+      <c r="T102" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq33映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±5分钟；反向位置物理seq28（站名待映射） ETA 0分钟参与校验</t>
+        </is>
+      </c>
       <c r="U102" s="2" t="inlineStr">
         <is>
           <t>19:30</t>
@@ -12680,7 +12704,7 @@
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P103" s="2" t="inlineStr">
@@ -12734,7 +12758,7 @@
       </c>
       <c r="AC103" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -12795,7 +12819,7 @@
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P104" s="2" t="inlineStr">
@@ -12910,7 +12934,7 @@
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P105" s="2" t="inlineStr">
@@ -13025,7 +13049,7 @@
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P106" s="2" t="inlineStr">
@@ -13079,7 +13103,7 @@
       </c>
       <c r="AC106" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -13140,7 +13164,7 @@
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P107" s="2" t="inlineStr">
@@ -13255,7 +13279,7 @@
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P108" s="2" t="inlineStr">
@@ -13304,12 +13328,12 @@
       </c>
       <c r="AB108" s="2" t="inlineStr">
         <is>
-          <t>128.7</t>
+          <t>129.7</t>
         </is>
       </c>
       <c r="AC108" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-27-浦东35路.xlsx
+++ b/data/export/2026-09-27-浦东35路.xlsx
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -951,17 +951,17 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>138.5</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>27/29</t>
+          <t>26/29</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1314,7 +1314,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1904,7 +1904,7 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>128.3</t>
+          <t>128.7</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
@@ -2220,7 +2220,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2264,17 +2264,17 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>130.5</t>
+          <t>128.7</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -2401,7 +2401,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -2462,7 +2462,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2819,7 +2819,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2873,7 +2873,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>26/29</t>
+          <t>27/29</t>
         </is>
       </c>
     </row>
@@ -2938,7 +2938,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -3057,7 +3057,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -3406,7 +3406,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -4120,7 +4120,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4283,17 +4283,17 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>138.5</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>27/29</t>
+          <t>26/29</t>
         </is>
       </c>
     </row>
@@ -4715,7 +4715,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4769,7 +4769,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -5076,7 +5076,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5125,7 +5125,7 @@
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>128.3</t>
+          <t>128.7</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
@@ -5195,7 +5195,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5314,7 +5314,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5358,17 +5358,17 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>130.5</t>
+          <t>128.7</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -5671,7 +5671,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5790,7 +5790,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5844,7 +5844,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>26/29</t>
+          <t>27/29</t>
         </is>
       </c>
     </row>
@@ -6028,7 +6028,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6147,7 +6147,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6201,7 +6201,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -6385,7 +6385,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6861,7 +6861,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -7637,7 +7637,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -7940,7 +7940,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -9257,7 +9257,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9306,7 +9306,7 @@
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>128.3</t>
+          <t>128.7</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
@@ -9491,7 +9491,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9535,17 +9535,17 @@
       </c>
       <c r="AA76" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>130.5</t>
+          <t>128.7</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -9664,7 +9664,7 @@
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -9729,7 +9729,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9783,7 +9783,7 @@
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>26/29</t>
+          <t>27/29</t>
         </is>
       </c>
     </row>
@@ -9848,7 +9848,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9892,17 +9892,17 @@
       </c>
       <c r="AA79" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>138.5</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>27/29</t>
+          <t>26/29</t>
         </is>
       </c>
     </row>
@@ -9963,7 +9963,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -10082,7 +10082,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10136,7 +10136,7 @@
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -10201,7 +10201,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10320,7 +10320,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10673,7 +10673,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -11506,7 +11506,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11560,7 +11560,7 @@
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -11955,24 +11955,24 @@
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>21:04</t>
+          <t>21:05</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>124分钟</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr"/>
       <c r="K97" s="2" t="inlineStr"/>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N97" s="2" t="inlineStr">
@@ -11982,7 +11982,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -12031,7 +12031,7 @@
       </c>
       <c r="AB97" s="2" t="inlineStr">
         <is>
-          <t>128.3</t>
+          <t>128.7</t>
         </is>
       </c>
       <c r="AC97" s="2" t="inlineStr">
@@ -12069,7 +12069,7 @@
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程49%处后消失；随后反向物理轨迹由seq28推进至seq50，推进22站，达到≥2站确认条件</t>
+          <t>原方向在全程49%处后消失；随后反向物理轨迹由seq28推进至seq62，推进34站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
@@ -12097,7 +12097,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12195,32 +12195,36 @@
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:26</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J99" s="2" t="inlineStr"/>
       <c r="K99" s="2" t="inlineStr"/>
       <c r="L99" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M99" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N99" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -12228,7 +12232,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12252,17 +12256,17 @@
       </c>
       <c r="W99" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X99" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y99" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z99" s="2" t="inlineStr">
@@ -12272,17 +12276,17 @@
       </c>
       <c r="AA99" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB99" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>138.5</t>
         </is>
       </c>
       <c r="AC99" s="2" t="inlineStr">
         <is>
-          <t>27/29</t>
+          <t>26/29</t>
         </is>
       </c>
     </row>
@@ -12310,32 +12314,36 @@
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:25</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr"/>
       <c r="K100" s="2" t="inlineStr"/>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M100" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N100" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -12343,7 +12351,7 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
@@ -12367,17 +12375,17 @@
       </c>
       <c r="W100" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X100" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y100" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z100" s="2" t="inlineStr">
@@ -12387,17 +12395,17 @@
       </c>
       <c r="AA100" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB100" s="2" t="inlineStr">
         <is>
-          <t>130.5</t>
+          <t>128.7</t>
         </is>
       </c>
       <c r="AC100" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -12512,7 +12520,7 @@
       </c>
       <c r="AC101" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -12545,7 +12553,7 @@
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程51%处后消失；随后反向物理轨迹由seq28推进至seq37，推进9站，达到≥2站确认条件</t>
+          <t>原方向在全程51%处后消失；随后反向物理轨迹由seq28推进至seq55，推进27站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
@@ -12573,7 +12581,7 @@
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
@@ -12704,7 +12712,7 @@
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P103" s="2" t="inlineStr">
@@ -12758,7 +12766,7 @@
       </c>
       <c r="AC103" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -12819,7 +12827,7 @@
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P104" s="2" t="inlineStr">
@@ -12873,7 +12881,7 @@
       </c>
       <c r="AC104" s="2" t="inlineStr">
         <is>
-          <t>26/29</t>
+          <t>27/29</t>
         </is>
       </c>
     </row>
@@ -12934,7 +12942,7 @@
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P105" s="2" t="inlineStr">
@@ -13049,7 +13057,7 @@
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P106" s="2" t="inlineStr">
@@ -13164,7 +13172,7 @@
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P107" s="2" t="inlineStr">
@@ -13279,7 +13287,7 @@
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P108" s="2" t="inlineStr">
@@ -13333,7 +13341,7 @@
       </c>
       <c r="AC108" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
